--- a/STT Report Elite Marketing FTMO June.xlsx
+++ b/STT Report Elite Marketing FTMO June.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EED91877-29F5-42CC-AECB-AC3F274F51EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA2E0F5E-FD20-4EE7-83D3-569A5FB2C8CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4AEE6371-F34D-490E-9664-B5033CDC9B85}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="265">
   <si>
     <t>Date</t>
   </si>
@@ -791,6 +791,39 @@
   </si>
   <si>
     <t>Mughalpura</t>
+  </si>
+  <si>
+    <t>Gourmet Food johar towm</t>
+  </si>
+  <si>
+    <t>Gourmet Food 12 G</t>
+  </si>
+  <si>
+    <t>Gourmet Food Fizaya</t>
+  </si>
+  <si>
+    <t>Gourmet Food Calvery</t>
+  </si>
+  <si>
+    <t>Galaxy Super Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lake City Mart </t>
+  </si>
+  <si>
+    <t>Joher Town</t>
+  </si>
+  <si>
+    <t>12 G Joher Town</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fizaya </t>
+  </si>
+  <si>
+    <t>Calevery Ground</t>
+  </si>
+  <si>
+    <t>lake caity</t>
   </si>
 </sst>
 </file>
@@ -1564,6 +1597,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1615,14 +1656,6 @@
     <xf numFmtId="0" fontId="17" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1973,114 +2006,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="89" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="89" t="s">
+      <c r="A1" s="93" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="93" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="90" t="s">
+      <c r="C1" s="94" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="90" t="s">
+      <c r="D1" s="94" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="90" t="s">
+      <c r="E1" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="90" t="s">
+      <c r="F1" s="94" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="89" t="s">
+      <c r="G1" s="93" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="90" t="s">
+      <c r="H1" s="94" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="71"/>
-      <c r="K1" s="89" t="s">
+      <c r="K1" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="89"/>
-      <c r="M1" s="89"/>
-      <c r="N1" s="89"/>
-      <c r="O1" s="94" t="s">
+      <c r="L1" s="93"/>
+      <c r="M1" s="93"/>
+      <c r="N1" s="93"/>
+      <c r="O1" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="95"/>
-      <c r="Q1" s="95"/>
-      <c r="R1" s="95"/>
-      <c r="S1" s="91" t="s">
+      <c r="P1" s="99"/>
+      <c r="Q1" s="99"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="93" t="s">
+      <c r="T1" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="93"/>
-      <c r="V1" s="93"/>
-      <c r="W1" s="93"/>
-      <c r="X1" s="93" t="s">
+      <c r="U1" s="97"/>
+      <c r="V1" s="97"/>
+      <c r="W1" s="97"/>
+      <c r="X1" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="93"/>
-      <c r="Z1" s="93"/>
-      <c r="AA1" s="93"/>
-      <c r="AB1" s="87" t="s">
+      <c r="Y1" s="97"/>
+      <c r="Z1" s="97"/>
+      <c r="AA1" s="97"/>
+      <c r="AB1" s="91" t="s">
         <v>76</v>
       </c>
-      <c r="AC1" s="87" t="s">
+      <c r="AC1" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="87" t="s">
+      <c r="AD1" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="87" t="s">
+      <c r="AE1" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="AF1" s="87" t="s">
+      <c r="AF1" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="AG1" s="87" t="s">
+      <c r="AG1" s="91" t="s">
         <v>17</v>
       </c>
       <c r="AH1" s="81">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="AI1" s="87" t="s">
+      <c r="AI1" s="91" t="s">
         <v>18</v>
       </c>
-      <c r="AJ1" s="87" t="s">
+      <c r="AJ1" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="87" t="s">
+      <c r="AK1" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="87" t="s">
+      <c r="AL1" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="87" t="s">
+      <c r="AM1" s="91" t="s">
         <v>22</v>
       </c>
-      <c r="AN1" s="85" t="s">
+      <c r="AN1" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="AO1" s="85" t="s">
+      <c r="AO1" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="AP1" s="87" t="s">
+      <c r="AP1" s="91" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:42" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="89"/>
-      <c r="B2" s="89"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="90"/>
+      <c r="A2" s="93"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="94"/>
       <c r="I2" s="2" t="s">
         <v>26</v>
       </c>
@@ -2111,7 +2144,7 @@
       <c r="R2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="S2" s="92"/>
+      <c r="S2" s="96"/>
       <c r="T2" s="4" t="s">
         <v>84</v>
       </c>
@@ -2136,23 +2169,23 @@
       <c r="AA2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="AB2" s="88"/>
-      <c r="AC2" s="88"/>
-      <c r="AD2" s="88"/>
-      <c r="AE2" s="88"/>
-      <c r="AF2" s="88"/>
-      <c r="AG2" s="88"/>
+      <c r="AB2" s="92"/>
+      <c r="AC2" s="92"/>
+      <c r="AD2" s="92"/>
+      <c r="AE2" s="92"/>
+      <c r="AF2" s="92"/>
+      <c r="AG2" s="92"/>
       <c r="AH2" s="79" t="s">
         <v>77</v>
       </c>
-      <c r="AI2" s="88"/>
-      <c r="AJ2" s="88"/>
-      <c r="AK2" s="88"/>
-      <c r="AL2" s="88"/>
-      <c r="AM2" s="88"/>
-      <c r="AN2" s="86"/>
-      <c r="AO2" s="86"/>
-      <c r="AP2" s="88"/>
+      <c r="AI2" s="92"/>
+      <c r="AJ2" s="92"/>
+      <c r="AK2" s="92"/>
+      <c r="AL2" s="92"/>
+      <c r="AM2" s="92"/>
+      <c r="AN2" s="90"/>
+      <c r="AO2" s="90"/>
+      <c r="AP2" s="92"/>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A3" s="18">
@@ -7115,13 +7148,13 @@
       <c r="E40" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F40" s="103" t="s">
+      <c r="F40" s="86" t="s">
         <v>224</v>
       </c>
-      <c r="G40" s="103" t="s">
+      <c r="G40" s="86" t="s">
         <v>225</v>
       </c>
-      <c r="H40" s="103" t="s">
+      <c r="H40" s="86" t="s">
         <v>228</v>
       </c>
       <c r="I40" s="70" t="s">
@@ -7130,23 +7163,23 @@
       <c r="J40" s="70">
         <v>800</v>
       </c>
-      <c r="K40" s="104">
+      <c r="K40" s="87">
         <v>800</v>
       </c>
-      <c r="L40" s="104">
+      <c r="L40" s="87">
         <v>800</v>
       </c>
-      <c r="M40" s="104">
+      <c r="M40" s="87">
         <v>800</v>
       </c>
       <c r="N40" s="9">
         <f t="shared" si="1"/>
         <v>2400</v>
       </c>
-      <c r="O40" s="102">
+      <c r="O40" s="85">
         <v>800</v>
       </c>
-      <c r="P40" s="102">
+      <c r="P40" s="85">
         <v>800</v>
       </c>
       <c r="Q40" s="19">
@@ -7248,13 +7281,13 @@
       <c r="E41" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F41" s="103" t="s">
+      <c r="F41" s="86" t="s">
         <v>224</v>
       </c>
-      <c r="G41" s="103" t="s">
+      <c r="G41" s="86" t="s">
         <v>226</v>
       </c>
-      <c r="H41" s="103" t="s">
+      <c r="H41" s="86" t="s">
         <v>228</v>
       </c>
       <c r="I41" s="70" t="s">
@@ -7263,23 +7296,23 @@
       <c r="J41" s="70">
         <v>80</v>
       </c>
-      <c r="K41" s="104">
+      <c r="K41" s="87">
         <v>80</v>
       </c>
-      <c r="L41" s="104">
+      <c r="L41" s="87">
         <v>80</v>
       </c>
-      <c r="M41" s="104">
+      <c r="M41" s="87">
         <v>80</v>
       </c>
       <c r="N41" s="9">
         <f t="shared" si="1"/>
         <v>240</v>
       </c>
-      <c r="O41" s="102">
+      <c r="O41" s="85">
         <v>80</v>
       </c>
-      <c r="P41" s="102">
+      <c r="P41" s="85">
         <v>80</v>
       </c>
       <c r="Q41" s="19">
@@ -7381,13 +7414,13 @@
       <c r="E42" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F42" s="103" t="s">
+      <c r="F42" s="86" t="s">
         <v>224</v>
       </c>
-      <c r="G42" s="103" t="s">
+      <c r="G42" s="86" t="s">
         <v>227</v>
       </c>
-      <c r="H42" s="103" t="s">
+      <c r="H42" s="86" t="s">
         <v>228</v>
       </c>
       <c r="I42" s="70" t="s">
@@ -7396,23 +7429,23 @@
       <c r="J42" s="70">
         <v>200</v>
       </c>
-      <c r="K42" s="104">
+      <c r="K42" s="87">
         <v>200</v>
       </c>
-      <c r="L42" s="104">
+      <c r="L42" s="87">
         <v>200</v>
       </c>
-      <c r="M42" s="104">
+      <c r="M42" s="87">
         <v>200</v>
       </c>
       <c r="N42" s="9">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="O42" s="102">
+      <c r="O42" s="85">
         <v>200</v>
       </c>
-      <c r="P42" s="102">
+      <c r="P42" s="85">
         <v>200</v>
       </c>
       <c r="Q42" s="19">
@@ -8169,13 +8202,13 @@
       <c r="E48" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F48" s="103" t="s">
+      <c r="F48" s="86" t="s">
         <v>224</v>
       </c>
-      <c r="G48" s="103" t="s">
+      <c r="G48" s="86" t="s">
         <v>229</v>
       </c>
-      <c r="H48" s="103" t="s">
+      <c r="H48" s="86" t="s">
         <v>228</v>
       </c>
       <c r="I48" s="70" t="s">
@@ -8183,16 +8216,16 @@
       </c>
       <c r="J48" s="70"/>
       <c r="K48" s="70"/>
-      <c r="L48" s="104"/>
-      <c r="M48" s="104"/>
+      <c r="L48" s="87"/>
+      <c r="M48" s="87"/>
       <c r="N48" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O48" s="102">
+      <c r="O48" s="85">
         <v>560</v>
       </c>
-      <c r="P48" s="104">
+      <c r="P48" s="87">
         <v>560</v>
       </c>
       <c r="Q48" s="19">
@@ -8294,13 +8327,13 @@
       <c r="E49" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F49" s="103" t="s">
+      <c r="F49" s="86" t="s">
         <v>224</v>
       </c>
-      <c r="G49" s="103" t="s">
+      <c r="G49" s="86" t="s">
         <v>230</v>
       </c>
-      <c r="H49" s="103" t="s">
+      <c r="H49" s="86" t="s">
         <v>228</v>
       </c>
       <c r="I49" s="70" t="s">
@@ -8310,20 +8343,20 @@
       <c r="K49" s="70">
         <v>1200</v>
       </c>
-      <c r="L49" s="104">
+      <c r="L49" s="87">
         <v>1200</v>
       </c>
-      <c r="M49" s="104">
+      <c r="M49" s="87">
         <v>1800</v>
       </c>
       <c r="N49" s="9">
         <f t="shared" si="1"/>
         <v>4200</v>
       </c>
-      <c r="O49" s="102">
+      <c r="O49" s="85">
         <v>2400</v>
       </c>
-      <c r="P49" s="104">
+      <c r="P49" s="87">
         <v>1800</v>
       </c>
       <c r="Q49" s="19">
@@ -10529,33 +10562,33 @@
       <c r="E66" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F66" s="103" t="s">
+      <c r="F66" s="86" t="s">
         <v>224</v>
       </c>
-      <c r="G66" s="103" t="s">
+      <c r="G66" s="86" t="s">
         <v>233</v>
       </c>
-      <c r="H66" s="103" t="s">
+      <c r="H66" s="86" t="s">
         <v>228</v>
       </c>
       <c r="I66" s="70" t="s">
         <v>235</v>
       </c>
       <c r="J66" s="70"/>
-      <c r="K66" s="104">
-        <v>0</v>
-      </c>
-      <c r="L66" s="104">
+      <c r="K66" s="87">
+        <v>0</v>
+      </c>
+      <c r="L66" s="87">
         <v>40</v>
       </c>
-      <c r="M66" s="104">
+      <c r="M66" s="87">
         <v>40</v>
       </c>
       <c r="N66" s="9">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="O66" s="102">
+      <c r="O66" s="85">
         <v>40</v>
       </c>
       <c r="P66" s="19">
@@ -10660,33 +10693,33 @@
       <c r="E67" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F67" s="103" t="s">
+      <c r="F67" s="86" t="s">
         <v>224</v>
       </c>
-      <c r="G67" s="103" t="s">
+      <c r="G67" s="86" t="s">
         <v>234</v>
       </c>
-      <c r="H67" s="103" t="s">
+      <c r="H67" s="86" t="s">
         <v>228</v>
       </c>
       <c r="I67" s="70" t="s">
         <v>236</v>
       </c>
       <c r="J67" s="70"/>
-      <c r="K67" s="104">
+      <c r="K67" s="87">
         <v>400</v>
       </c>
-      <c r="L67" s="104">
+      <c r="L67" s="87">
         <v>200</v>
       </c>
-      <c r="M67" s="104">
+      <c r="M67" s="87">
         <v>400</v>
       </c>
       <c r="N67" s="9">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="O67" s="102">
+      <c r="O67" s="85">
         <v>400</v>
       </c>
       <c r="P67" s="19">
@@ -12653,13 +12686,13 @@
       <c r="E82" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F82" s="103" t="s">
+      <c r="F82" s="86" t="s">
         <v>224</v>
       </c>
-      <c r="G82" s="103" t="s">
+      <c r="G82" s="86" t="s">
         <v>158</v>
       </c>
-      <c r="H82" s="103" t="s">
+      <c r="H82" s="86" t="s">
         <v>228</v>
       </c>
       <c r="I82" s="70" t="s">
@@ -12784,13 +12817,13 @@
       <c r="E83" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F83" s="103" t="s">
+      <c r="F83" s="86" t="s">
         <v>224</v>
       </c>
-      <c r="G83" s="103" t="s">
+      <c r="G83" s="86" t="s">
         <v>237</v>
       </c>
-      <c r="H83" s="103" t="s">
+      <c r="H83" s="86" t="s">
         <v>228</v>
       </c>
       <c r="I83" s="70" t="s">
@@ -12915,13 +12948,13 @@
       <c r="E84" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F84" s="103" t="s">
+      <c r="F84" s="86" t="s">
         <v>224</v>
       </c>
-      <c r="G84" s="103" t="s">
+      <c r="G84" s="86" t="s">
         <v>238</v>
       </c>
-      <c r="H84" s="103" t="s">
+      <c r="H84" s="86" t="s">
         <v>228</v>
       </c>
       <c r="I84" s="70" t="s">
@@ -13046,13 +13079,13 @@
       <c r="E85" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F85" s="103" t="s">
+      <c r="F85" s="86" t="s">
         <v>224</v>
       </c>
-      <c r="G85" s="103" t="s">
+      <c r="G85" s="86" t="s">
         <v>239</v>
       </c>
-      <c r="H85" s="103" t="s">
+      <c r="H85" s="86" t="s">
         <v>228</v>
       </c>
       <c r="I85" s="70" t="s">
@@ -14773,13 +14806,13 @@
       <c r="E98" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F98" s="103" t="s">
+      <c r="F98" s="86" t="s">
         <v>224</v>
       </c>
-      <c r="G98" s="103" t="s">
+      <c r="G98" s="86" t="s">
         <v>243</v>
       </c>
-      <c r="H98" s="103" t="s">
+      <c r="H98" s="86" t="s">
         <v>228</v>
       </c>
       <c r="I98" s="70" t="s">
@@ -14788,27 +14821,27 @@
       <c r="J98" s="70">
         <v>40</v>
       </c>
-      <c r="K98" s="102">
+      <c r="K98" s="85">
         <v>40</v>
       </c>
-      <c r="L98" s="104"/>
-      <c r="M98" s="104">
+      <c r="L98" s="87"/>
+      <c r="M98" s="87">
         <v>40</v>
       </c>
       <c r="N98" s="9">
         <f t="shared" si="55"/>
         <v>80</v>
       </c>
-      <c r="O98" s="102">
-        <v>0</v>
-      </c>
-      <c r="P98" s="104">
-        <v>0</v>
-      </c>
-      <c r="Q98" s="104">
+      <c r="O98" s="85">
+        <v>0</v>
+      </c>
+      <c r="P98" s="87">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="87">
         <v>80</v>
       </c>
-      <c r="R98" s="105">
+      <c r="R98" s="88">
         <f t="shared" si="46"/>
         <v>80</v>
       </c>
@@ -14904,42 +14937,42 @@
       <c r="E99" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F99" s="103" t="s">
+      <c r="F99" s="86" t="s">
         <v>224</v>
       </c>
-      <c r="G99" s="103" t="s">
+      <c r="G99" s="86" t="s">
         <v>230</v>
       </c>
-      <c r="H99" s="103" t="s">
+      <c r="H99" s="86" t="s">
         <v>228</v>
       </c>
       <c r="I99" s="70" t="s">
         <v>246</v>
       </c>
       <c r="J99" s="70"/>
-      <c r="K99" s="102">
+      <c r="K99" s="85">
         <v>600</v>
       </c>
-      <c r="L99" s="104">
+      <c r="L99" s="87">
         <v>597</v>
       </c>
-      <c r="M99" s="104">
+      <c r="M99" s="87">
         <v>797</v>
       </c>
       <c r="N99" s="9">
         <f t="shared" si="55"/>
         <v>1994</v>
       </c>
-      <c r="O99" s="102">
+      <c r="O99" s="85">
         <v>1597</v>
       </c>
-      <c r="P99" s="104">
+      <c r="P99" s="87">
         <v>1184</v>
       </c>
-      <c r="Q99" s="104">
+      <c r="Q99" s="87">
         <v>1199</v>
       </c>
-      <c r="R99" s="105">
+      <c r="R99" s="88">
         <f t="shared" si="46"/>
         <v>3980</v>
       </c>
@@ -15035,38 +15068,38 @@
       <c r="E100" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F100" s="103" t="s">
+      <c r="F100" s="86" t="s">
         <v>224</v>
       </c>
-      <c r="G100" s="103" t="s">
+      <c r="G100" s="86" t="s">
         <v>244</v>
       </c>
-      <c r="H100" s="103" t="s">
+      <c r="H100" s="86" t="s">
         <v>228</v>
       </c>
       <c r="I100" s="70" t="s">
         <v>157</v>
       </c>
       <c r="J100" s="70"/>
-      <c r="K100" s="102"/>
-      <c r="L100" s="104"/>
-      <c r="M100" s="104">
+      <c r="K100" s="85"/>
+      <c r="L100" s="87"/>
+      <c r="M100" s="87">
         <v>40</v>
       </c>
       <c r="N100" s="9">
         <f t="shared" si="55"/>
         <v>40</v>
       </c>
-      <c r="O100" s="102">
+      <c r="O100" s="85">
         <v>40</v>
       </c>
-      <c r="P100" s="104">
+      <c r="P100" s="87">
         <v>40</v>
       </c>
-      <c r="Q100" s="104">
+      <c r="Q100" s="87">
         <v>40</v>
       </c>
-      <c r="R100" s="105">
+      <c r="R100" s="88">
         <f t="shared" si="46"/>
         <v>120</v>
       </c>
@@ -15162,42 +15195,42 @@
       <c r="E101" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F101" s="103" t="s">
+      <c r="F101" s="86" t="s">
         <v>224</v>
       </c>
-      <c r="G101" s="103" t="s">
+      <c r="G101" s="86" t="s">
         <v>158</v>
       </c>
-      <c r="H101" s="103" t="s">
+      <c r="H101" s="86" t="s">
         <v>228</v>
       </c>
       <c r="I101" s="70" t="s">
         <v>157</v>
       </c>
       <c r="J101" s="70"/>
-      <c r="K101" s="102">
+      <c r="K101" s="85">
         <v>40</v>
       </c>
-      <c r="L101" s="104">
+      <c r="L101" s="87">
         <v>40</v>
       </c>
-      <c r="M101" s="104">
+      <c r="M101" s="87">
         <v>40</v>
       </c>
       <c r="N101" s="9">
         <f t="shared" si="55"/>
         <v>120</v>
       </c>
-      <c r="O101" s="102">
+      <c r="O101" s="85">
         <v>40</v>
       </c>
-      <c r="P101" s="104">
+      <c r="P101" s="87">
         <v>40</v>
       </c>
-      <c r="Q101" s="104">
+      <c r="Q101" s="87">
         <v>40</v>
       </c>
-      <c r="R101" s="105">
+      <c r="R101" s="88">
         <f t="shared" si="46"/>
         <v>120</v>
       </c>
@@ -16623,39 +16656,39 @@
       <c r="E112" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F112" s="103" t="s">
+      <c r="F112" s="86" t="s">
         <v>224</v>
       </c>
-      <c r="G112" s="103" t="s">
+      <c r="G112" s="86" t="s">
         <v>247</v>
       </c>
-      <c r="H112" s="103" t="s">
+      <c r="H112" s="86" t="s">
         <v>228</v>
       </c>
       <c r="I112" s="70" t="s">
         <v>248</v>
       </c>
       <c r="J112" s="70"/>
-      <c r="K112" s="102">
+      <c r="K112" s="85">
         <v>120</v>
       </c>
-      <c r="L112" s="102">
+      <c r="L112" s="85">
         <v>120</v>
       </c>
-      <c r="M112" s="102">
+      <c r="M112" s="85">
         <v>120</v>
       </c>
       <c r="N112" s="9">
         <f t="shared" si="55"/>
         <v>360</v>
       </c>
-      <c r="O112" s="102">
+      <c r="O112" s="85">
         <v>120</v>
       </c>
-      <c r="P112" s="102">
+      <c r="P112" s="85">
         <v>120</v>
       </c>
-      <c r="Q112" s="102">
+      <c r="Q112" s="85">
         <v>120</v>
       </c>
       <c r="R112" s="9">
@@ -16754,39 +16787,39 @@
       <c r="E113" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F113" s="103" t="s">
+      <c r="F113" s="86" t="s">
         <v>224</v>
       </c>
-      <c r="G113" s="103" t="s">
+      <c r="G113" s="86" t="s">
         <v>247</v>
       </c>
-      <c r="H113" s="103" t="s">
+      <c r="H113" s="86" t="s">
         <v>228</v>
       </c>
       <c r="I113" s="70" t="s">
         <v>248</v>
       </c>
       <c r="J113" s="70"/>
-      <c r="K113" s="102">
+      <c r="K113" s="85">
         <v>300</v>
       </c>
-      <c r="L113" s="102">
+      <c r="L113" s="85">
         <v>300</v>
       </c>
-      <c r="M113" s="102">
+      <c r="M113" s="85">
         <v>300</v>
       </c>
       <c r="N113" s="9">
         <f t="shared" si="55"/>
         <v>900</v>
       </c>
-      <c r="O113" s="102">
+      <c r="O113" s="85">
         <v>300</v>
       </c>
-      <c r="P113" s="102">
+      <c r="P113" s="85">
         <v>300</v>
       </c>
-      <c r="Q113" s="102">
+      <c r="Q113" s="85">
         <v>300</v>
       </c>
       <c r="R113" s="9">
@@ -16930,35 +16963,35 @@
         <v>60</v>
       </c>
       <c r="T114" s="19">
-        <f t="shared" ref="T112:T114" si="65">K114/10</f>
+        <f t="shared" ref="T114" si="65">K114/10</f>
         <v>30</v>
       </c>
       <c r="U114" s="19">
-        <f t="shared" ref="U112:U114" si="66">L114/10</f>
+        <f t="shared" ref="U114" si="66">L114/10</f>
         <v>30</v>
       </c>
       <c r="V114" s="19">
-        <f t="shared" ref="V112:V114" si="67">M114/10</f>
+        <f t="shared" ref="V114" si="67">M114/10</f>
         <v>30</v>
       </c>
       <c r="W114" s="9">
-        <f t="shared" ref="W112:W114" si="68">N114/10</f>
+        <f t="shared" ref="W114" si="68">N114/10</f>
         <v>90</v>
       </c>
       <c r="X114" s="19">
-        <f t="shared" ref="X112:X114" si="69">O114/10</f>
+        <f t="shared" ref="X114" si="69">O114/10</f>
         <v>5</v>
       </c>
       <c r="Y114" s="19">
-        <f t="shared" ref="Y112:Y114" si="70">P114/10</f>
+        <f t="shared" ref="Y114" si="70">P114/10</f>
         <v>4</v>
       </c>
       <c r="Z114" s="19">
-        <f t="shared" ref="Z112:Z114" si="71">Q114/10</f>
+        <f t="shared" ref="Z114" si="71">Q114/10</f>
         <v>2</v>
       </c>
       <c r="AA114" s="9">
-        <f t="shared" ref="AA112:AA114" si="72">R114/10</f>
+        <f t="shared" ref="AA114" si="72">R114/10</f>
         <v>11</v>
       </c>
       <c r="AB114" s="9">
@@ -16971,33 +17004,33 @@
         <v>72.64</v>
       </c>
       <c r="AE114" s="10">
-        <f t="shared" ref="AE112:AE114" si="73">(J114*AB114)+(N114*AC114)+(AD114*S114)</f>
+        <f t="shared" ref="AE114" si="73">(J114*AB114)+(N114*AC114)+(AD114*S114)</f>
         <v>52360.05</v>
       </c>
       <c r="AF114" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG114" s="11">
-        <f t="shared" ref="AG112:AG114" si="74">AE114*AF114</f>
+        <f t="shared" ref="AG114" si="74">AE114*AF114</f>
         <v>3403.4032500000003</v>
       </c>
       <c r="AH114" s="80">
-        <f t="shared" ref="AH112:AH114" si="75">(AB114*J114)*$AH$1</f>
+        <f t="shared" ref="AH114" si="75">(AB114*J114)*$AH$1</f>
         <v>27.489000000000004</v>
       </c>
       <c r="AI114" s="10">
-        <f t="shared" ref="AI112:AI114" si="76">AE114-AG114</f>
+        <f t="shared" ref="AI114" si="76">AE114-AG114</f>
         <v>48956.64675</v>
       </c>
       <c r="AJ114" s="5">
         <v>0.18</v>
       </c>
       <c r="AK114" s="12">
-        <f t="shared" ref="AK112:AK114" si="77">AI114*AJ114</f>
+        <f t="shared" ref="AK114" si="77">AI114*AJ114</f>
         <v>8812.1964150000003</v>
       </c>
       <c r="AL114" s="10">
-        <f t="shared" ref="AL112:AL114" si="78">AI114+AK114</f>
+        <f t="shared" ref="AL114" si="78">AI114+AK114</f>
         <v>57768.843164999998</v>
       </c>
       <c r="AP114" s="13"/>
@@ -19939,7 +19972,7 @@
         <v>1125</v>
       </c>
       <c r="D137" s="82">
-        <v>43493.630952381303</v>
+        <v>43440.392857143299</v>
       </c>
       <c r="E137" s="6" t="s">
         <v>79</v>
@@ -20066,11 +20099,11 @@
       <c r="B138" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="C138" s="19">
-        <v>1125</v>
+      <c r="C138" s="82">
+        <v>1126.1428571428601</v>
       </c>
       <c r="D138" s="82">
-        <v>43467.011904762301</v>
+        <v>43440.392857143299</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>79</v>
@@ -20193,62 +20226,94 @@
       <c r="AP138" s="13"/>
     </row>
     <row r="139" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A139" s="18"/>
-      <c r="C139" s="19"/>
-      <c r="E139" s="6"/>
-      <c r="F139" s="20"/>
-      <c r="G139" s="20"/>
-      <c r="H139" s="20"/>
-      <c r="I139" s="6"/>
+      <c r="A139" s="18">
+        <v>46189</v>
+      </c>
+      <c r="B139" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C139" s="82">
+        <v>1126.6428571428601</v>
+      </c>
+      <c r="D139" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E139" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F139" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="G139" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="H139" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="I139" s="6" t="s">
+        <v>260</v>
+      </c>
       <c r="J139" s="70"/>
-      <c r="K139" s="21"/>
-      <c r="L139" s="21"/>
-      <c r="M139" s="21"/>
+      <c r="K139" s="21">
+        <v>80</v>
+      </c>
+      <c r="L139" s="21">
+        <v>80</v>
+      </c>
+      <c r="M139" s="21">
+        <v>80</v>
+      </c>
       <c r="N139" s="9">
         <f t="shared" si="87"/>
-        <v>0</v>
-      </c>
-      <c r="O139" s="19"/>
-      <c r="P139" s="21"/>
-      <c r="Q139" s="21"/>
+        <v>240</v>
+      </c>
+      <c r="O139" s="19">
+        <v>80</v>
+      </c>
+      <c r="P139" s="21">
+        <v>80</v>
+      </c>
+      <c r="Q139" s="21">
+        <v>80</v>
+      </c>
       <c r="R139" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="S139" s="19">
         <v>20</v>
       </c>
       <c r="T139" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U139" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V139" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W139" s="9">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X139" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y139" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z139" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA139" s="9">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB139" s="9">
         <v>39.270000000000003</v>
@@ -20261,14 +20326,14 @@
       </c>
       <c r="AE139" s="10">
         <f t="shared" si="58"/>
-        <v>1452.8</v>
+        <v>14043.8</v>
       </c>
       <c r="AF139" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG139" s="11">
         <f t="shared" si="86"/>
-        <v>94.432000000000002</v>
+        <v>912.84699999999998</v>
       </c>
       <c r="AH139" s="80">
         <f t="shared" si="59"/>
@@ -20276,78 +20341,110 @@
       </c>
       <c r="AI139" s="10">
         <f t="shared" si="60"/>
-        <v>1358.3679999999999</v>
+        <v>13130.953</v>
       </c>
       <c r="AJ139" s="5">
         <v>0.18</v>
       </c>
       <c r="AK139" s="12">
         <f t="shared" si="61"/>
-        <v>244.50623999999999</v>
+        <v>2363.5715399999999</v>
       </c>
       <c r="AL139" s="10">
         <f t="shared" si="62"/>
-        <v>1602.8742399999999</v>
+        <v>15494.524539999999</v>
       </c>
       <c r="AP139" s="13"/>
     </row>
     <row r="140" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A140" s="18"/>
-      <c r="C140" s="19"/>
-      <c r="E140" s="6"/>
-      <c r="F140" s="20"/>
-      <c r="G140" s="20"/>
-      <c r="H140" s="20"/>
-      <c r="I140" s="6"/>
+      <c r="A140" s="18">
+        <v>46189</v>
+      </c>
+      <c r="B140" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C140" s="82">
+        <v>1127.1428571428601</v>
+      </c>
+      <c r="D140" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E140" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F140" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="G140" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="H140" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="I140" s="6" t="s">
+        <v>261</v>
+      </c>
       <c r="J140" s="70"/>
-      <c r="K140" s="21"/>
-      <c r="L140" s="21"/>
-      <c r="M140" s="21"/>
+      <c r="K140" s="21">
+        <v>80</v>
+      </c>
+      <c r="L140" s="21">
+        <v>80</v>
+      </c>
+      <c r="M140" s="21">
+        <v>80</v>
+      </c>
       <c r="N140" s="9">
         <f t="shared" si="87"/>
-        <v>0</v>
-      </c>
-      <c r="O140" s="19"/>
-      <c r="P140" s="19"/>
-      <c r="Q140" s="19"/>
+        <v>240</v>
+      </c>
+      <c r="O140" s="19">
+        <v>80</v>
+      </c>
+      <c r="P140" s="19">
+        <v>80</v>
+      </c>
+      <c r="Q140" s="19">
+        <v>80</v>
+      </c>
       <c r="R140" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="S140" s="19">
         <v>40</v>
       </c>
       <c r="T140" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U140" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V140" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W140" s="9">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X140" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y140" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z140" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA140" s="9">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB140" s="9">
         <v>39.270000000000003</v>
@@ -20360,14 +20457,14 @@
       </c>
       <c r="AE140" s="10">
         <f t="shared" si="58"/>
-        <v>2905.6</v>
+        <v>15496.6</v>
       </c>
       <c r="AF140" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG140" s="11">
         <f t="shared" si="86"/>
-        <v>188.864</v>
+        <v>1007.2790000000001</v>
       </c>
       <c r="AH140" s="80">
         <f t="shared" si="59"/>
@@ -20375,78 +20472,110 @@
       </c>
       <c r="AI140" s="10">
         <f t="shared" si="60"/>
-        <v>2716.7359999999999</v>
+        <v>14489.321</v>
       </c>
       <c r="AJ140" s="5">
         <v>0.18</v>
       </c>
       <c r="AK140" s="12">
         <f t="shared" si="61"/>
-        <v>489.01247999999998</v>
+        <v>2608.0777800000001</v>
       </c>
       <c r="AL140" s="10">
         <f t="shared" si="62"/>
-        <v>3205.7484799999997</v>
+        <v>17097.39878</v>
       </c>
       <c r="AP140" s="13"/>
     </row>
     <row r="141" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A141" s="18"/>
-      <c r="C141" s="19"/>
-      <c r="E141" s="6"/>
-      <c r="F141" s="20"/>
-      <c r="G141" s="20"/>
-      <c r="H141" s="20"/>
-      <c r="I141" s="6"/>
+      <c r="A141" s="18">
+        <v>46189</v>
+      </c>
+      <c r="B141" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C141" s="82">
+        <v>1127.6428571428601</v>
+      </c>
+      <c r="D141" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E141" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F141" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="G141" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="H141" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="I141" s="6" t="s">
+        <v>262</v>
+      </c>
       <c r="J141" s="70"/>
-      <c r="K141" s="21"/>
-      <c r="L141" s="21"/>
-      <c r="M141" s="21"/>
+      <c r="K141" s="21">
+        <v>80</v>
+      </c>
+      <c r="L141" s="21">
+        <v>80</v>
+      </c>
+      <c r="M141" s="21">
+        <v>80</v>
+      </c>
       <c r="N141" s="9">
         <f t="shared" si="87"/>
-        <v>0</v>
-      </c>
-      <c r="O141" s="19"/>
-      <c r="P141" s="21"/>
-      <c r="Q141" s="19"/>
+        <v>240</v>
+      </c>
+      <c r="O141" s="19">
+        <v>80</v>
+      </c>
+      <c r="P141" s="21">
+        <v>80</v>
+      </c>
+      <c r="Q141" s="19">
+        <v>80</v>
+      </c>
       <c r="R141" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="S141" s="19">
         <v>2</v>
       </c>
       <c r="T141" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U141" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V141" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W141" s="9">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X141" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y141" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z141" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA141" s="9">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB141" s="9">
         <v>39.270000000000003</v>
@@ -20459,14 +20588,14 @@
       </c>
       <c r="AE141" s="10">
         <f t="shared" si="58"/>
-        <v>145.28</v>
+        <v>12736.28</v>
       </c>
       <c r="AF141" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG141" s="11">
         <f t="shared" si="86"/>
-        <v>9.4432000000000009</v>
+        <v>827.85820000000012</v>
       </c>
       <c r="AH141" s="80">
         <f t="shared" si="59"/>
@@ -20474,78 +20603,110 @@
       </c>
       <c r="AI141" s="10">
         <f t="shared" si="60"/>
-        <v>135.83680000000001</v>
+        <v>11908.4218</v>
       </c>
       <c r="AJ141" s="5">
         <v>0.18</v>
       </c>
       <c r="AK141" s="12">
         <f t="shared" si="61"/>
-        <v>24.450624000000001</v>
+        <v>2143.5159239999998</v>
       </c>
       <c r="AL141" s="10">
         <f t="shared" si="62"/>
-        <v>160.28742400000002</v>
+        <v>14051.937723999999</v>
       </c>
       <c r="AP141" s="13"/>
     </row>
     <row r="142" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A142" s="18"/>
-      <c r="C142" s="19"/>
-      <c r="E142" s="6"/>
-      <c r="F142" s="20"/>
-      <c r="G142" s="20"/>
-      <c r="H142" s="20"/>
-      <c r="I142" s="6"/>
+      <c r="A142" s="18">
+        <v>46189</v>
+      </c>
+      <c r="B142" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C142" s="82">
+        <v>1128.1428571428601</v>
+      </c>
+      <c r="D142" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E142" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F142" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="G142" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="H142" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="I142" s="6" t="s">
+        <v>263</v>
+      </c>
       <c r="J142" s="70"/>
-      <c r="K142" s="19"/>
-      <c r="L142" s="21"/>
-      <c r="M142" s="21"/>
+      <c r="K142" s="19">
+        <v>40</v>
+      </c>
+      <c r="L142" s="21">
+        <v>40</v>
+      </c>
+      <c r="M142" s="21">
+        <v>40</v>
+      </c>
       <c r="N142" s="9">
         <f t="shared" si="87"/>
-        <v>0</v>
-      </c>
-      <c r="O142" s="19"/>
-      <c r="P142" s="19"/>
-      <c r="Q142" s="21"/>
+        <v>120</v>
+      </c>
+      <c r="O142" s="19">
+        <v>40</v>
+      </c>
+      <c r="P142" s="19">
+        <v>40</v>
+      </c>
+      <c r="Q142" s="21">
+        <v>40</v>
+      </c>
       <c r="R142" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S142" s="19">
         <v>40</v>
       </c>
       <c r="T142" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U142" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V142" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W142" s="9">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="X142" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y142" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z142" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA142" s="9">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB142" s="9">
         <v>39.270000000000003</v>
@@ -20558,14 +20719,14 @@
       </c>
       <c r="AE142" s="10">
         <f t="shared" si="58"/>
-        <v>2905.6</v>
+        <v>9201.1</v>
       </c>
       <c r="AF142" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG142" s="11">
         <f t="shared" si="86"/>
-        <v>188.864</v>
+        <v>598.07150000000001</v>
       </c>
       <c r="AH142" s="80">
         <f t="shared" si="59"/>
@@ -20573,78 +20734,112 @@
       </c>
       <c r="AI142" s="10">
         <f t="shared" si="60"/>
-        <v>2716.7359999999999</v>
+        <v>8603.0285000000003</v>
       </c>
       <c r="AJ142" s="5">
         <v>0.18</v>
       </c>
       <c r="AK142" s="12">
         <f t="shared" si="61"/>
-        <v>489.01247999999998</v>
+        <v>1548.54513</v>
       </c>
       <c r="AL142" s="10">
         <f t="shared" si="62"/>
-        <v>3205.7484799999997</v>
+        <v>10151.573630000001</v>
       </c>
       <c r="AP142" s="13"/>
     </row>
     <row r="143" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A143" s="18"/>
-      <c r="C143" s="19"/>
-      <c r="E143" s="6"/>
-      <c r="F143" s="20"/>
-      <c r="G143" s="20"/>
-      <c r="H143" s="20"/>
-      <c r="I143" s="6"/>
-      <c r="J143" s="70"/>
-      <c r="K143" s="21"/>
-      <c r="L143" s="21"/>
-      <c r="M143" s="21"/>
+      <c r="A143" s="18">
+        <v>46189</v>
+      </c>
+      <c r="B143" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C143" s="82">
+        <v>1128.6428571428601</v>
+      </c>
+      <c r="D143" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E143" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F143" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="G143" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="H143" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="I143" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="J143" s="70">
+        <v>80</v>
+      </c>
+      <c r="K143" s="21">
+        <v>80</v>
+      </c>
+      <c r="L143" s="21">
+        <v>80</v>
+      </c>
+      <c r="M143" s="21">
+        <v>80</v>
+      </c>
       <c r="N143" s="9">
         <f t="shared" si="87"/>
-        <v>0</v>
-      </c>
-      <c r="O143" s="19"/>
-      <c r="P143" s="21"/>
-      <c r="Q143" s="19"/>
+        <v>240</v>
+      </c>
+      <c r="O143" s="19">
+        <v>80</v>
+      </c>
+      <c r="P143" s="21">
+        <v>80</v>
+      </c>
+      <c r="Q143" s="19">
+        <v>80</v>
+      </c>
       <c r="R143" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="S143" s="19">
         <v>20</v>
       </c>
       <c r="T143" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U143" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V143" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W143" s="9">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X143" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y143" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z143" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA143" s="9">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB143" s="9">
         <v>39.270000000000003</v>
@@ -20657,93 +20852,127 @@
       </c>
       <c r="AE143" s="10">
         <f t="shared" si="58"/>
-        <v>1452.8</v>
+        <v>17185.400000000001</v>
       </c>
       <c r="AF143" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG143" s="11">
         <f t="shared" si="86"/>
-        <v>94.432000000000002</v>
+        <v>1117.0510000000002</v>
       </c>
       <c r="AH143" s="80">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>109.95600000000002</v>
       </c>
       <c r="AI143" s="10">
         <f t="shared" si="60"/>
-        <v>1358.3679999999999</v>
+        <v>16068.349000000002</v>
       </c>
       <c r="AJ143" s="5">
         <v>0.18</v>
       </c>
       <c r="AK143" s="12">
         <f t="shared" si="61"/>
-        <v>244.50623999999999</v>
+        <v>2892.3028200000003</v>
       </c>
       <c r="AL143" s="10">
         <f t="shared" si="62"/>
-        <v>1602.8742399999999</v>
+        <v>18960.651820000003</v>
       </c>
       <c r="AP143" s="13"/>
     </row>
     <row r="144" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A144" s="18"/>
-      <c r="C144" s="19"/>
-      <c r="E144" s="6"/>
-      <c r="F144" s="20"/>
-      <c r="G144" s="20"/>
-      <c r="H144" s="20"/>
-      <c r="I144" s="6"/>
-      <c r="J144" s="70"/>
-      <c r="K144" s="19"/>
-      <c r="L144" s="21"/>
-      <c r="M144" s="19"/>
+      <c r="A144" s="18">
+        <v>46189</v>
+      </c>
+      <c r="B144" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C144" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D144" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E144" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F144" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="G144" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="H144" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="I144" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="J144" s="70">
+        <v>120</v>
+      </c>
+      <c r="K144" s="19">
+        <v>120</v>
+      </c>
+      <c r="L144" s="21">
+        <v>120</v>
+      </c>
+      <c r="M144" s="19">
+        <v>120</v>
+      </c>
       <c r="N144" s="9">
         <f t="shared" si="87"/>
-        <v>0</v>
-      </c>
-      <c r="O144" s="19"/>
-      <c r="P144" s="19"/>
-      <c r="Q144" s="19"/>
+        <v>360</v>
+      </c>
+      <c r="O144" s="19">
+        <v>120</v>
+      </c>
+      <c r="P144" s="19">
+        <v>120</v>
+      </c>
+      <c r="Q144" s="19">
+        <v>120</v>
+      </c>
       <c r="R144" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="S144" s="19">
         <v>100</v>
       </c>
       <c r="T144" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U144" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V144" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W144" s="9">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="X144" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y144" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z144" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA144" s="9">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AB144" s="9">
         <v>39.270000000000003</v>
@@ -20756,33 +20985,33 @@
       </c>
       <c r="AE144" s="10">
         <f t="shared" si="58"/>
-        <v>7264</v>
+        <v>30862.9</v>
       </c>
       <c r="AF144" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG144" s="11">
         <f t="shared" si="86"/>
-        <v>472.16</v>
+        <v>2006.0885000000001</v>
       </c>
       <c r="AH144" s="80">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>164.93400000000003</v>
       </c>
       <c r="AI144" s="10">
         <f t="shared" si="60"/>
-        <v>6791.84</v>
+        <v>28856.8115</v>
       </c>
       <c r="AJ144" s="5">
         <v>0.18</v>
       </c>
       <c r="AK144" s="12">
         <f t="shared" si="61"/>
-        <v>1222.5311999999999</v>
+        <v>5194.2260699999997</v>
       </c>
       <c r="AL144" s="10">
         <f t="shared" si="62"/>
-        <v>8014.3711999999996</v>
+        <v>34051.03757</v>
       </c>
       <c r="AP144" s="13"/>
     </row>
@@ -49505,104 +49734,104 @@
       <c r="H435" s="6"/>
       <c r="I435" s="6"/>
       <c r="J435" s="6">
-        <f>SUM(J3:J434)</f>
-        <v>4443</v>
+        <f t="shared" ref="J435:AA435" si="176">SUM(J3:J434)</f>
+        <v>4643</v>
       </c>
       <c r="K435" s="6">
-        <f>SUM(K3:K434)</f>
-        <v>10255</v>
+        <f t="shared" si="176"/>
+        <v>10735</v>
       </c>
       <c r="L435" s="6">
-        <f>SUM(L3:L434)</f>
-        <v>8517</v>
+        <f t="shared" si="176"/>
+        <v>8997</v>
       </c>
       <c r="M435" s="6">
-        <f>SUM(M3:M434)</f>
-        <v>11364</v>
+        <f t="shared" si="176"/>
+        <v>11844</v>
       </c>
       <c r="N435" s="6">
-        <f>SUM(N3:N434)</f>
-        <v>30136</v>
+        <f t="shared" si="176"/>
+        <v>31576</v>
       </c>
       <c r="O435" s="6">
-        <f>SUM(O3:O434)</f>
-        <v>13787</v>
+        <f t="shared" si="176"/>
+        <v>14267</v>
       </c>
       <c r="P435" s="6">
-        <f>SUM(P3:P434)</f>
-        <v>11972</v>
+        <f t="shared" si="176"/>
+        <v>12452</v>
       </c>
       <c r="Q435" s="6">
-        <f>SUM(Q3:Q434)</f>
-        <v>19414</v>
+        <f t="shared" si="176"/>
+        <v>19894</v>
       </c>
       <c r="R435" s="6">
-        <f>SUM(R3:R434)</f>
-        <v>45173</v>
+        <f t="shared" si="176"/>
+        <v>46613</v>
       </c>
       <c r="S435" s="6">
-        <f>SUM(S3:S434)</f>
+        <f t="shared" si="176"/>
         <v>40138</v>
       </c>
       <c r="T435" s="6">
-        <f>SUM(T3:T434)</f>
-        <v>1025.1000000000004</v>
+        <f t="shared" si="176"/>
+        <v>1073.1000000000004</v>
       </c>
       <c r="U435" s="6">
-        <f>SUM(U3:U434)</f>
-        <v>851.40000000000043</v>
+        <f t="shared" si="176"/>
+        <v>899.40000000000043</v>
       </c>
       <c r="V435" s="6">
-        <f>SUM(V3:V434)</f>
-        <v>1136.25</v>
+        <f t="shared" si="176"/>
+        <v>1184.25</v>
       </c>
       <c r="W435" s="6">
-        <f>SUM(W3:W434)</f>
-        <v>3012.7499999999991</v>
+        <f t="shared" si="176"/>
+        <v>3156.7499999999991</v>
       </c>
       <c r="X435" s="6">
-        <f>SUM(X3:X434)</f>
-        <v>1378.6999999999998</v>
+        <f t="shared" si="176"/>
+        <v>1426.6999999999998</v>
       </c>
       <c r="Y435" s="6">
-        <f>SUM(Y3:Y434)</f>
-        <v>1197.2000000000003</v>
+        <f t="shared" si="176"/>
+        <v>1245.2000000000003</v>
       </c>
       <c r="Z435" s="6">
-        <f>SUM(Z3:Z434)</f>
-        <v>1941.4</v>
+        <f t="shared" si="176"/>
+        <v>1989.4</v>
       </c>
       <c r="AA435" s="6">
-        <f>SUM(AA3:AA434)</f>
-        <v>4517.2999999999993</v>
+        <f t="shared" si="176"/>
+        <v>4661.2999999999993</v>
       </c>
       <c r="AB435" s="6"/>
       <c r="AC435" s="6"/>
       <c r="AD435" s="6"/>
       <c r="AE435" s="6">
         <f>SUM(AE3:AE434)</f>
-        <v>4671110.8300000029</v>
+        <v>4754510.8300000029</v>
       </c>
       <c r="AF435" s="8"/>
       <c r="AG435" s="6">
         <f>SUM(AG3:AG434)</f>
-        <v>382399.45836729952</v>
+        <v>387820.45836729929</v>
       </c>
       <c r="AH435" s="6">
         <f>SUM(AH3:AH434)</f>
-        <v>6106.6813499999989</v>
+        <v>6381.5713499999993</v>
       </c>
       <c r="AI435" s="6">
         <f>SUM(AI3:AI434)</f>
-        <v>4288642.6491326997</v>
+        <v>4366621.6491327025</v>
       </c>
       <c r="AK435" s="6">
         <f>SUM(AK3:AK434)</f>
-        <v>771955.67684388661</v>
+        <v>785991.89684388658</v>
       </c>
       <c r="AL435" s="6">
         <f>SUM(AL3:AL434)</f>
-        <v>5060598.3259765822</v>
+        <v>5152613.5459765792</v>
       </c>
       <c r="AP435" s="13"/>
     </row>
@@ -49678,92 +49907,92 @@
         <v>55</v>
       </c>
       <c r="J439" s="77">
-        <f t="shared" ref="J439:AF439" si="176">+J435/40</f>
-        <v>111.075</v>
+        <f t="shared" ref="J439:AF439" si="177">+J435/40</f>
+        <v>116.075</v>
       </c>
       <c r="K439" s="78">
-        <f t="shared" si="176"/>
-        <v>256.375</v>
+        <f t="shared" si="177"/>
+        <v>268.375</v>
       </c>
       <c r="L439" s="78">
-        <f t="shared" si="176"/>
-        <v>212.92500000000001</v>
+        <f t="shared" si="177"/>
+        <v>224.92500000000001</v>
       </c>
       <c r="M439" s="78">
-        <f t="shared" si="176"/>
-        <v>284.10000000000002</v>
+        <f t="shared" si="177"/>
+        <v>296.10000000000002</v>
       </c>
       <c r="N439" s="77">
-        <f t="shared" si="176"/>
-        <v>753.4</v>
+        <f t="shared" si="177"/>
+        <v>789.4</v>
       </c>
       <c r="O439" s="78">
-        <f t="shared" si="176"/>
-        <v>344.67500000000001</v>
+        <f t="shared" si="177"/>
+        <v>356.67500000000001</v>
       </c>
       <c r="P439" s="78">
-        <f t="shared" si="176"/>
-        <v>299.3</v>
+        <f t="shared" si="177"/>
+        <v>311.3</v>
       </c>
       <c r="Q439" s="78">
-        <f t="shared" si="176"/>
-        <v>485.35</v>
+        <f t="shared" si="177"/>
+        <v>497.35</v>
       </c>
       <c r="R439" s="77">
-        <f t="shared" si="176"/>
-        <v>1129.325</v>
+        <f t="shared" si="177"/>
+        <v>1165.325</v>
       </c>
       <c r="S439" s="16">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>1003.45</v>
       </c>
       <c r="T439" s="16">
-        <f t="shared" si="176"/>
-        <v>25.627500000000008</v>
+        <f t="shared" si="177"/>
+        <v>26.827500000000008</v>
       </c>
       <c r="U439" s="16">
-        <f t="shared" si="176"/>
-        <v>21.285000000000011</v>
+        <f t="shared" si="177"/>
+        <v>22.48500000000001</v>
       </c>
       <c r="V439" s="16">
-        <f t="shared" si="176"/>
-        <v>28.40625</v>
+        <f t="shared" si="177"/>
+        <v>29.606249999999999</v>
       </c>
       <c r="W439" s="16">
-        <f t="shared" si="176"/>
-        <v>75.31874999999998</v>
+        <f t="shared" si="177"/>
+        <v>78.918749999999974</v>
       </c>
       <c r="X439" s="16">
-        <f t="shared" si="176"/>
-        <v>34.467499999999994</v>
+        <f t="shared" si="177"/>
+        <v>35.667499999999997</v>
       </c>
       <c r="Y439" s="16">
-        <f t="shared" si="176"/>
-        <v>29.930000000000007</v>
+        <f t="shared" si="177"/>
+        <v>31.130000000000006</v>
       </c>
       <c r="Z439" s="16">
-        <f t="shared" si="176"/>
-        <v>48.535000000000004</v>
+        <f t="shared" si="177"/>
+        <v>49.734999999999999</v>
       </c>
       <c r="AA439" s="16">
-        <f t="shared" si="176"/>
-        <v>112.93249999999998</v>
+        <f t="shared" si="177"/>
+        <v>116.53249999999998</v>
       </c>
       <c r="AB439" s="16"/>
       <c r="AC439">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="AD439">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="AE439">
-        <f t="shared" si="176"/>
-        <v>116777.77075000007</v>
+        <f t="shared" si="177"/>
+        <v>118862.77075000007</v>
       </c>
       <c r="AF439">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
     </row>
@@ -49841,22 +50070,22 @@
   <sheetData>
     <row r="3" spans="4:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="4:8" ht="22.5" thickBot="1" x14ac:dyDescent="0.7">
-      <c r="D4" s="96" t="s">
+      <c r="D4" s="100" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="97"/>
-      <c r="F4" s="97"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="98"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="102"/>
     </row>
     <row r="5" spans="4:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D5" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="E5" s="99"/>
-      <c r="F5" s="99"/>
-      <c r="G5" s="99"/>
-      <c r="H5" s="99"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="103"/>
+      <c r="H5" s="103"/>
     </row>
     <row r="6" spans="4:8" x14ac:dyDescent="0.35">
       <c r="D6" s="24" t="s">
@@ -49885,11 +50114,11 @@
       <c r="F7" s="29"/>
       <c r="G7" s="30">
         <f>('STT Report'!O435+'STT Report'!X435)/40</f>
-        <v>379.14250000000004</v>
+        <v>392.34250000000003</v>
       </c>
       <c r="H7" s="31">
         <f>E7+F7-G7</f>
-        <v>304.07749999999999</v>
+        <v>290.8775</v>
       </c>
     </row>
     <row r="8" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -49904,11 +50133,11 @@
       </c>
       <c r="G8" s="30">
         <f>('STT Report'!P435+'STT Report'!Y435)/40</f>
-        <v>329.23</v>
+        <v>342.43</v>
       </c>
       <c r="H8" s="31">
         <f>E8+F8-G8</f>
-        <v>4.42999999999995</v>
+        <v>-8.7700000000000387</v>
       </c>
     </row>
     <row r="9" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -49921,11 +50150,11 @@
       <c r="F9" s="32"/>
       <c r="G9" s="30">
         <f>('STT Report'!Q435+'STT Report'!Z435)/40</f>
-        <v>533.88499999999999</v>
+        <v>547.08500000000004</v>
       </c>
       <c r="H9" s="31">
         <f>E9+F9-G9</f>
-        <v>-199.02499999999998</v>
+        <v>-212.22500000000002</v>
       </c>
     </row>
     <row r="10" spans="4:8" x14ac:dyDescent="0.35">
@@ -49942,11 +50171,11 @@
       </c>
       <c r="G10" s="36">
         <f>SUM(G7:G9)</f>
-        <v>1242.2575000000002</v>
+        <v>1281.8575000000001</v>
       </c>
       <c r="H10" s="37">
         <f>SUM(H7:H9)</f>
-        <v>109.48249999999996</v>
+        <v>69.882499999999936</v>
       </c>
     </row>
     <row r="11" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -49959,11 +50188,11 @@
       </c>
       <c r="G11" s="73">
         <f>'STT Report'!J435/40</f>
-        <v>111.075</v>
+        <v>116.075</v>
       </c>
       <c r="H11" s="31">
         <f t="shared" ref="H11:H13" si="0">(E11+F11)-G11</f>
-        <v>388.92500000000001</v>
+        <v>383.92500000000001</v>
       </c>
     </row>
     <row r="12" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -49997,11 +50226,11 @@
       </c>
       <c r="G14" s="34">
         <f>SUM(G11:G13)</f>
-        <v>111.075</v>
+        <v>116.075</v>
       </c>
       <c r="H14" s="37">
         <f>SUM(H11:H13)</f>
-        <v>388.92500000000001</v>
+        <v>383.92500000000001</v>
       </c>
     </row>
     <row r="15" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -50014,11 +50243,11 @@
       <c r="F15" s="29"/>
       <c r="G15" s="30">
         <f>('STT Report'!K435+'STT Report'!T435)/40</f>
-        <v>282.0025</v>
+        <v>295.20249999999999</v>
       </c>
       <c r="H15" s="31">
         <f>E15+F15-G15</f>
-        <v>-53.882499999999993</v>
+        <v>-67.082499999999982</v>
       </c>
     </row>
     <row r="16" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -50031,11 +50260,11 @@
       <c r="F16" s="32"/>
       <c r="G16" s="30">
         <f>('STT Report'!L435+'STT Report'!U435)/40</f>
-        <v>234.20999999999998</v>
+        <v>247.41</v>
       </c>
       <c r="H16" s="31">
         <f>E16+F16-G16</f>
-        <v>87.28000000000003</v>
+        <v>74.080000000000013</v>
       </c>
     </row>
     <row r="17" spans="3:13" ht="16.5" x14ac:dyDescent="0.45">
@@ -50050,11 +50279,11 @@
       </c>
       <c r="G17" s="30">
         <f>('STT Report'!M435+'STT Report'!V435)/40</f>
-        <v>312.50625000000002</v>
+        <v>325.70625000000001</v>
       </c>
       <c r="H17" s="31">
         <f>E17+F17-G17</f>
-        <v>-80.18625000000003</v>
+        <v>-93.386250000000018</v>
       </c>
     </row>
     <row r="18" spans="3:13" x14ac:dyDescent="0.35">
@@ -50071,11 +50300,11 @@
       </c>
       <c r="G18" s="36">
         <f>SUM(G15:G17)</f>
-        <v>828.71875</v>
+        <v>868.31874999999991</v>
       </c>
       <c r="H18" s="37">
         <f>SUM(H15:H17)</f>
-        <v>-46.788749999999993</v>
+        <v>-86.388749999999987</v>
       </c>
     </row>
     <row r="19" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -50092,11 +50321,11 @@
       </c>
       <c r="G19" s="39">
         <f>G10+G14+G18</f>
-        <v>2182.0512500000004</v>
+        <v>2266.2512500000003</v>
       </c>
       <c r="H19" s="41">
         <f>H10+H14+H18</f>
-        <v>451.61874999999998</v>
+        <v>367.41874999999993</v>
       </c>
     </row>
     <row r="20" spans="3:13" x14ac:dyDescent="0.35">
@@ -50328,10 +50557,10 @@
       </c>
     </row>
     <row r="28" spans="3:13" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C28" s="100" t="s">
+      <c r="C28" s="104" t="s">
         <v>70</v>
       </c>
-      <c r="D28" s="101"/>
+      <c r="D28" s="105"/>
       <c r="E28" s="65">
         <f t="shared" ref="E28:L28" si="4">SUM(E24:E27)</f>
         <v>2500</v>

--- a/STT Report Elite Marketing FTMO June.xlsx
+++ b/STT Report Elite Marketing FTMO June.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA2E0F5E-FD20-4EE7-83D3-569A5FB2C8CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ADE4628-64E3-418C-9DE9-1D53DCDF5041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4AEE6371-F34D-490E-9664-B5033CDC9B85}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="325">
   <si>
     <t>Date</t>
   </si>
@@ -825,6 +825,186 @@
   <si>
     <t>lake caity</t>
   </si>
+  <si>
+    <t xml:space="preserve">Imran Pan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kanah Mandi </t>
+  </si>
+  <si>
+    <t>Mazang</t>
+  </si>
+  <si>
+    <t>ShadBagh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hikma </t>
+  </si>
+  <si>
+    <t>Express</t>
+  </si>
+  <si>
+    <t>haider</t>
+  </si>
+  <si>
+    <t>mian</t>
+  </si>
+  <si>
+    <t>Askari 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bismilla </t>
+  </si>
+  <si>
+    <t>nishat</t>
+  </si>
+  <si>
+    <t>Bin Sohan</t>
+  </si>
+  <si>
+    <t>Bin Daud</t>
+  </si>
+  <si>
+    <t>Ahmad Store</t>
+  </si>
+  <si>
+    <t>jameel Store</t>
+  </si>
+  <si>
+    <t>Tahir Store</t>
+  </si>
+  <si>
+    <t>Nishat colony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Larance Bakery </t>
+  </si>
+  <si>
+    <t>Quality Store</t>
+  </si>
+  <si>
+    <t>Chiragh din Road</t>
+  </si>
+  <si>
+    <t>Kacha Larnes Road</t>
+  </si>
+  <si>
+    <t>Smart Pharmacy</t>
+  </si>
+  <si>
+    <t>Askari Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bin Doud </t>
+  </si>
+  <si>
+    <t>Askari 9</t>
+  </si>
+  <si>
+    <t>Khan Store</t>
+  </si>
+  <si>
+    <t>My Store</t>
+  </si>
+  <si>
+    <t>Bakhtawer Store</t>
+  </si>
+  <si>
+    <t>Lala g Super Store</t>
+  </si>
+  <si>
+    <t>Makkah Colony</t>
+  </si>
+  <si>
+    <t>MB Traders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crown </t>
+  </si>
+  <si>
+    <t>Risan Askari 11</t>
+  </si>
+  <si>
+    <t>Gourmet Shalamar Link</t>
+  </si>
+  <si>
+    <t>Gourmet Shadbagh</t>
+  </si>
+  <si>
+    <t>Gourmet Bata Pur</t>
+  </si>
+  <si>
+    <t>Gourmet Salamat Pura</t>
+  </si>
+  <si>
+    <t>Gourmet Daroghawala</t>
+  </si>
+  <si>
+    <t>Gourmet Railway Palaza</t>
+  </si>
+  <si>
+    <t>Gourmet Taj Bagh</t>
+  </si>
+  <si>
+    <t>Gourmet Taj Pura</t>
+  </si>
+  <si>
+    <t>Gourmet Baghban Pura</t>
+  </si>
+  <si>
+    <t>Gourmet Sultan Pura</t>
+  </si>
+  <si>
+    <t>Gourmet Shadi Pura</t>
+  </si>
+  <si>
+    <t>Gourmet Manawa GT Road</t>
+  </si>
+  <si>
+    <t>Shalamar Link</t>
+  </si>
+  <si>
+    <t>Shadbagh</t>
+  </si>
+  <si>
+    <t>Bata Pur</t>
+  </si>
+  <si>
+    <t>Salamat Pura</t>
+  </si>
+  <si>
+    <t>Daroghawala</t>
+  </si>
+  <si>
+    <t>Railway Palaza</t>
+  </si>
+  <si>
+    <t>Taj Bagh</t>
+  </si>
+  <si>
+    <t>Taj Pura</t>
+  </si>
+  <si>
+    <t>Baghban Pura</t>
+  </si>
+  <si>
+    <t>Sultan Pura</t>
+  </si>
+  <si>
+    <t>Shadi Pura</t>
+  </si>
+  <si>
+    <t>Manawa GT Road</t>
+  </si>
+  <si>
+    <t>Askari 11</t>
+  </si>
+  <si>
+    <t>GT Road</t>
+  </si>
+  <si>
+    <t>Singh Pura</t>
+  </si>
 </sst>
 </file>
 
@@ -1605,22 +1785,22 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="4" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1632,11 +1812,11 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1985,7 +2165,7 @@
     <col min="6" max="6" width="13.26953125" customWidth="1"/>
     <col min="7" max="7" width="42.453125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21" customWidth="1"/>
-    <col min="9" max="9" width="11.6328125" customWidth="1"/>
+    <col min="9" max="9" width="23.7265625" bestFit="1" customWidth="1"/>
     <col min="10" max="18" width="8.1796875" customWidth="1"/>
     <col min="19" max="19" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="20" max="28" width="8.1796875" customWidth="1"/>
@@ -2006,44 +2186,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="93" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="93" t="s">
+      <c r="A1" s="92" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="92" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="94" t="s">
+      <c r="C1" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="94" t="s">
+      <c r="D1" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="94" t="s">
+      <c r="E1" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="94" t="s">
+      <c r="F1" s="89" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="93" t="s">
+      <c r="G1" s="92" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="94" t="s">
+      <c r="H1" s="89" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="71"/>
-      <c r="K1" s="93" t="s">
+      <c r="K1" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="93"/>
-      <c r="M1" s="93"/>
-      <c r="N1" s="93"/>
-      <c r="O1" s="98" t="s">
+      <c r="L1" s="92"/>
+      <c r="M1" s="92"/>
+      <c r="N1" s="92"/>
+      <c r="O1" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+      <c r="R1" s="91"/>
       <c r="S1" s="95" t="s">
         <v>10</v>
       </c>
@@ -2059,61 +2239,61 @@
       <c r="Y1" s="97"/>
       <c r="Z1" s="97"/>
       <c r="AA1" s="97"/>
-      <c r="AB1" s="91" t="s">
+      <c r="AB1" s="93" t="s">
         <v>76</v>
       </c>
-      <c r="AC1" s="91" t="s">
+      <c r="AC1" s="93" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="91" t="s">
+      <c r="AD1" s="93" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="91" t="s">
+      <c r="AE1" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="AF1" s="91" t="s">
+      <c r="AF1" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="AG1" s="91" t="s">
+      <c r="AG1" s="93" t="s">
         <v>17</v>
       </c>
       <c r="AH1" s="81">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="AI1" s="91" t="s">
+      <c r="AI1" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="AJ1" s="91" t="s">
+      <c r="AJ1" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="91" t="s">
+      <c r="AK1" s="93" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="91" t="s">
+      <c r="AL1" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="91" t="s">
+      <c r="AM1" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="AN1" s="89" t="s">
+      <c r="AN1" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="AO1" s="89" t="s">
+      <c r="AO1" s="98" t="s">
         <v>24</v>
       </c>
-      <c r="AP1" s="91" t="s">
+      <c r="AP1" s="93" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:42" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="93"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="94"/>
+      <c r="A2" s="92"/>
+      <c r="B2" s="92"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="89"/>
       <c r="I2" s="2" t="s">
         <v>26</v>
       </c>
@@ -2169,23 +2349,23 @@
       <c r="AA2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="AB2" s="92"/>
-      <c r="AC2" s="92"/>
-      <c r="AD2" s="92"/>
-      <c r="AE2" s="92"/>
-      <c r="AF2" s="92"/>
-      <c r="AG2" s="92"/>
+      <c r="AB2" s="94"/>
+      <c r="AC2" s="94"/>
+      <c r="AD2" s="94"/>
+      <c r="AE2" s="94"/>
+      <c r="AF2" s="94"/>
+      <c r="AG2" s="94"/>
       <c r="AH2" s="79" t="s">
         <v>77</v>
       </c>
-      <c r="AI2" s="92"/>
-      <c r="AJ2" s="92"/>
-      <c r="AK2" s="92"/>
-      <c r="AL2" s="92"/>
-      <c r="AM2" s="92"/>
-      <c r="AN2" s="90"/>
-      <c r="AO2" s="90"/>
-      <c r="AP2" s="92"/>
+      <c r="AI2" s="94"/>
+      <c r="AJ2" s="94"/>
+      <c r="AK2" s="94"/>
+      <c r="AL2" s="94"/>
+      <c r="AM2" s="94"/>
+      <c r="AN2" s="99"/>
+      <c r="AO2" s="99"/>
+      <c r="AP2" s="94"/>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A3" s="18">
@@ -21016,62 +21196,96 @@
       <c r="AP144" s="13"/>
     </row>
     <row r="145" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A145" s="18"/>
-      <c r="C145" s="19"/>
-      <c r="E145" s="6"/>
-      <c r="F145" s="20"/>
-      <c r="G145" s="20"/>
-      <c r="H145" s="20"/>
-      <c r="I145" s="6"/>
-      <c r="J145" s="70"/>
-      <c r="K145" s="19"/>
-      <c r="L145" s="19"/>
-      <c r="M145" s="19"/>
+      <c r="A145" s="18">
+        <v>46189</v>
+      </c>
+      <c r="B145" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C145" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D145" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E145" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F145" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G145" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="H145" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="I145" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="J145" s="70">
+        <v>12</v>
+      </c>
+      <c r="K145" s="19">
+        <v>14</v>
+      </c>
+      <c r="L145" s="19">
+        <v>7</v>
+      </c>
+      <c r="M145" s="19">
+        <v>6</v>
+      </c>
       <c r="N145" s="9">
         <f t="shared" si="87"/>
-        <v>0</v>
-      </c>
-      <c r="O145" s="21"/>
-      <c r="P145" s="21"/>
-      <c r="Q145" s="21"/>
+        <v>27</v>
+      </c>
+      <c r="O145" s="21">
+        <v>16</v>
+      </c>
+      <c r="P145" s="21">
+        <v>20</v>
+      </c>
+      <c r="Q145" s="21">
+        <v>21</v>
+      </c>
       <c r="R145" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="S145" s="19">
         <v>40</v>
       </c>
       <c r="T145" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="U145" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="V145" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W145" s="9">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X145" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y145" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z145" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA145" s="9">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AB145" s="9">
         <v>39.270000000000003</v>
@@ -21084,93 +21298,127 @@
       </c>
       <c r="AE145" s="10">
         <f t="shared" si="58"/>
-        <v>2905.6</v>
+        <v>4793.3274999999994</v>
       </c>
       <c r="AF145" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG145" s="11">
         <f t="shared" si="86"/>
-        <v>188.864</v>
+        <v>311.56628749999999</v>
       </c>
       <c r="AH145" s="80">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>16.493400000000001</v>
       </c>
       <c r="AI145" s="10">
         <f t="shared" si="60"/>
-        <v>2716.7359999999999</v>
+        <v>4481.7612124999996</v>
       </c>
       <c r="AJ145" s="5">
         <v>0.18</v>
       </c>
       <c r="AK145" s="12">
         <f t="shared" si="61"/>
-        <v>489.01247999999998</v>
+        <v>806.71701824999991</v>
       </c>
       <c r="AL145" s="10">
         <f t="shared" si="62"/>
-        <v>3205.7484799999997</v>
+        <v>5288.4782307499991</v>
       </c>
       <c r="AP145" s="13"/>
     </row>
     <row r="146" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A146" s="18"/>
-      <c r="C146" s="19"/>
-      <c r="E146" s="6"/>
-      <c r="F146" s="20"/>
-      <c r="G146" s="20"/>
-      <c r="H146" s="20"/>
-      <c r="I146" s="6"/>
-      <c r="J146" s="70"/>
-      <c r="K146" s="21"/>
-      <c r="L146" s="21"/>
-      <c r="M146" s="21"/>
+      <c r="A146" s="18">
+        <v>46189</v>
+      </c>
+      <c r="B146" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C146" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D146" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E146" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F146" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G146" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="H146" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="I146" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="J146" s="70">
+        <v>12</v>
+      </c>
+      <c r="K146" s="21">
+        <v>20</v>
+      </c>
+      <c r="L146" s="21">
+        <v>12</v>
+      </c>
+      <c r="M146" s="21">
+        <v>7</v>
+      </c>
       <c r="N146" s="9">
         <f t="shared" si="87"/>
-        <v>0</v>
-      </c>
-      <c r="O146" s="19"/>
-      <c r="P146" s="21"/>
-      <c r="Q146" s="21"/>
+        <v>39</v>
+      </c>
+      <c r="O146" s="19">
+        <v>40</v>
+      </c>
+      <c r="P146" s="21">
+        <v>20</v>
+      </c>
+      <c r="Q146" s="21">
+        <v>20</v>
+      </c>
       <c r="R146" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S146" s="19">
         <v>40</v>
       </c>
       <c r="T146" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U146" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V146" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W146" s="9">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="X146" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y146" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z146" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA146" s="9">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AB146" s="9">
         <v>39.270000000000003</v>
@@ -21183,93 +21431,127 @@
       </c>
       <c r="AE146" s="10">
         <f t="shared" si="58"/>
-        <v>2905.6</v>
+        <v>5422.8775000000005</v>
       </c>
       <c r="AF146" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG146" s="11">
         <f t="shared" si="86"/>
-        <v>188.864</v>
+        <v>352.48703750000004</v>
       </c>
       <c r="AH146" s="80">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>16.493400000000001</v>
       </c>
       <c r="AI146" s="10">
         <f t="shared" si="60"/>
-        <v>2716.7359999999999</v>
+        <v>5070.3904625000005</v>
       </c>
       <c r="AJ146" s="5">
         <v>0.18</v>
       </c>
       <c r="AK146" s="12">
         <f t="shared" si="61"/>
-        <v>489.01247999999998</v>
+        <v>912.67028325000001</v>
       </c>
       <c r="AL146" s="10">
         <f t="shared" si="62"/>
-        <v>3205.7484799999997</v>
+        <v>5983.0607457500009</v>
       </c>
       <c r="AP146" s="13"/>
     </row>
     <row r="147" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A147" s="18"/>
-      <c r="C147" s="19"/>
-      <c r="E147" s="6"/>
-      <c r="F147" s="20"/>
-      <c r="G147" s="20"/>
-      <c r="H147" s="20"/>
-      <c r="I147" s="6"/>
-      <c r="J147" s="70"/>
-      <c r="K147" s="19"/>
-      <c r="L147" s="19"/>
-      <c r="M147" s="19"/>
+      <c r="A147" s="18">
+        <v>46189</v>
+      </c>
+      <c r="B147" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C147" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D147" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F147" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G147" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="H147" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="I147" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="J147" s="70">
+        <v>0</v>
+      </c>
+      <c r="K147" s="19">
+        <v>20</v>
+      </c>
+      <c r="L147" s="19">
+        <v>6</v>
+      </c>
+      <c r="M147" s="19">
+        <v>12</v>
+      </c>
       <c r="N147" s="9">
         <f t="shared" si="87"/>
-        <v>0</v>
-      </c>
-      <c r="O147" s="19"/>
-      <c r="P147" s="19"/>
-      <c r="Q147" s="19"/>
+        <v>38</v>
+      </c>
+      <c r="O147" s="19">
+        <v>40</v>
+      </c>
+      <c r="P147" s="19">
+        <v>21</v>
+      </c>
+      <c r="Q147" s="19">
+        <v>60</v>
+      </c>
       <c r="R147" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="S147" s="19">
         <v>80</v>
       </c>
       <c r="T147" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U147" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="V147" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W147" s="9">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X147" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y147" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z147" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA147" s="9">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="AB147" s="9">
         <v>39.270000000000003</v>
@@ -21282,14 +21564,14 @@
       </c>
       <c r="AE147" s="10">
         <f t="shared" si="58"/>
-        <v>5811.2</v>
+        <v>7804.7749999999996</v>
       </c>
       <c r="AF147" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG147" s="11">
         <f t="shared" si="86"/>
-        <v>377.72800000000001</v>
+        <v>507.31037500000002</v>
       </c>
       <c r="AH147" s="80">
         <f t="shared" si="59"/>
@@ -21297,66 +21579,100 @@
       </c>
       <c r="AI147" s="10">
         <f t="shared" si="60"/>
-        <v>5433.4719999999998</v>
+        <v>7297.4646249999996</v>
       </c>
       <c r="AJ147" s="5">
         <v>0.18</v>
       </c>
       <c r="AK147" s="12">
         <f t="shared" si="61"/>
-        <v>978.02495999999996</v>
+        <v>1313.5436324999998</v>
       </c>
       <c r="AL147" s="10">
         <f t="shared" si="62"/>
-        <v>6411.4969599999995</v>
+        <v>8611.0082574999997</v>
       </c>
       <c r="AP147" s="13"/>
     </row>
     <row r="148" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A148" s="18"/>
-      <c r="C148" s="19"/>
-      <c r="E148" s="6"/>
-      <c r="F148" s="20"/>
-      <c r="G148" s="20"/>
-      <c r="H148" s="20"/>
-      <c r="I148" s="6"/>
-      <c r="J148" s="70"/>
-      <c r="K148" s="19"/>
-      <c r="L148" s="19"/>
-      <c r="M148" s="19"/>
+      <c r="A148" s="18">
+        <v>46189</v>
+      </c>
+      <c r="B148" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C148" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D148" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E148" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F148" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G148" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="H148" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="I148" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="J148" s="70">
+        <v>40</v>
+      </c>
+      <c r="K148" s="19">
+        <v>10</v>
+      </c>
+      <c r="L148" s="19">
+        <v>7</v>
+      </c>
+      <c r="M148" s="19">
+        <v>20</v>
+      </c>
       <c r="N148" s="9">
         <f t="shared" si="87"/>
-        <v>0</v>
-      </c>
-      <c r="O148" s="21"/>
-      <c r="P148" s="21"/>
-      <c r="Q148" s="21"/>
+        <v>37</v>
+      </c>
+      <c r="O148" s="21">
+        <v>10</v>
+      </c>
+      <c r="P148" s="21">
+        <v>0</v>
+      </c>
+      <c r="Q148" s="21">
+        <v>5</v>
+      </c>
       <c r="R148" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S148" s="19">
         <v>40</v>
       </c>
       <c r="T148" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U148" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="V148" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W148" s="9">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="X148" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y148" s="19">
         <f t="shared" si="84"/>
@@ -21364,11 +21680,11 @@
       </c>
       <c r="Z148" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AA148" s="9">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB148" s="9">
         <v>39.270000000000003</v>
@@ -21381,81 +21697,115 @@
       </c>
       <c r="AE148" s="10">
         <f t="shared" si="58"/>
-        <v>2905.6</v>
+        <v>6417.5125000000007</v>
       </c>
       <c r="AF148" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG148" s="11">
         <f t="shared" si="86"/>
-        <v>188.864</v>
+        <v>417.13831250000004</v>
       </c>
       <c r="AH148" s="80">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI148" s="10">
         <f t="shared" si="60"/>
-        <v>2716.7359999999999</v>
+        <v>6000.3741875000005</v>
       </c>
       <c r="AJ148" s="5">
         <v>0.18</v>
       </c>
       <c r="AK148" s="12">
         <f t="shared" si="61"/>
-        <v>489.01247999999998</v>
+        <v>1080.0673537500002</v>
       </c>
       <c r="AL148" s="10">
         <f t="shared" si="62"/>
-        <v>3205.7484799999997</v>
+        <v>7080.4415412500002</v>
       </c>
       <c r="AP148" s="13"/>
     </row>
     <row r="149" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A149" s="18"/>
-      <c r="C149" s="19"/>
-      <c r="E149" s="6"/>
-      <c r="F149" s="20"/>
-      <c r="G149" s="20"/>
-      <c r="H149" s="20"/>
-      <c r="I149" s="6"/>
-      <c r="J149" s="70"/>
-      <c r="K149" s="21"/>
-      <c r="L149" s="21"/>
-      <c r="M149" s="21"/>
+      <c r="A149" s="18">
+        <v>46189</v>
+      </c>
+      <c r="B149" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C149" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D149" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E149" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F149" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G149" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="H149" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="I149" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="J149" s="70">
+        <v>40</v>
+      </c>
+      <c r="K149" s="21">
+        <v>10</v>
+      </c>
+      <c r="L149" s="21">
+        <v>18</v>
+      </c>
+      <c r="M149" s="21">
+        <v>20</v>
+      </c>
       <c r="N149" s="9">
         <f t="shared" ref="N149:N212" si="88">SUM(K149:M149)</f>
-        <v>0</v>
-      </c>
-      <c r="O149" s="19"/>
-      <c r="P149" s="19"/>
-      <c r="Q149" s="19"/>
+        <v>48</v>
+      </c>
+      <c r="O149" s="19">
+        <v>10</v>
+      </c>
+      <c r="P149" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q149" s="19">
+        <v>5</v>
+      </c>
       <c r="R149" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S149" s="19">
         <v>40</v>
       </c>
       <c r="T149" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U149" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V149" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W149" s="9">
         <f t="shared" ref="W149:W212" si="89">N149/10</f>
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="X149" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y149" s="19">
         <f t="shared" si="84"/>
@@ -21463,11 +21813,11 @@
       </c>
       <c r="Z149" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AA149" s="9">
         <f t="shared" ref="AA149:AA212" si="90">R149/10</f>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB149" s="9">
         <v>39.270000000000003</v>
@@ -21480,77 +21830,111 @@
       </c>
       <c r="AE149" s="10">
         <f t="shared" ref="AE149:AE212" si="91">(J149*AB149)+(N149*AC149)+(AD149*S149)</f>
-        <v>2905.6</v>
+        <v>6994.6</v>
       </c>
       <c r="AF149" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG149" s="11">
         <f t="shared" si="86"/>
-        <v>188.864</v>
+        <v>454.64900000000006</v>
       </c>
       <c r="AH149" s="80">
         <f t="shared" ref="AH149:AH212" si="92">(AB149*J149)*$AH$1</f>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI149" s="10">
         <f t="shared" ref="AI149:AI212" si="93">AE149-AG149</f>
-        <v>2716.7359999999999</v>
+        <v>6539.951</v>
       </c>
       <c r="AJ149" s="5">
         <v>0.18</v>
       </c>
       <c r="AK149" s="12">
         <f t="shared" ref="AK149:AK212" si="94">AI149*AJ149</f>
-        <v>489.01247999999998</v>
+        <v>1177.19118</v>
       </c>
       <c r="AL149" s="10">
         <f t="shared" ref="AL149:AL212" si="95">AI149+AK149</f>
-        <v>3205.7484799999997</v>
+        <v>7717.1421799999998</v>
       </c>
       <c r="AP149" s="13"/>
     </row>
     <row r="150" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A150" s="18"/>
-      <c r="C150" s="19"/>
-      <c r="E150" s="6"/>
-      <c r="F150" s="20"/>
-      <c r="G150" s="20"/>
-      <c r="H150" s="20"/>
-      <c r="I150" s="6"/>
-      <c r="J150" s="70"/>
-      <c r="K150" s="19"/>
-      <c r="L150" s="19"/>
-      <c r="M150" s="21"/>
+      <c r="A150" s="18">
+        <v>46189</v>
+      </c>
+      <c r="B150" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C150" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D150" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E150" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F150" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G150" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="H150" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="I150" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="J150" s="70">
+        <v>20</v>
+      </c>
+      <c r="K150" s="19">
+        <v>10</v>
+      </c>
+      <c r="L150" s="19">
+        <v>10</v>
+      </c>
+      <c r="M150" s="21">
+        <v>2</v>
+      </c>
       <c r="N150" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O150" s="19"/>
-      <c r="P150" s="21"/>
-      <c r="Q150" s="19"/>
+        <v>22</v>
+      </c>
+      <c r="O150" s="19">
+        <v>0</v>
+      </c>
+      <c r="P150" s="21">
+        <v>10</v>
+      </c>
+      <c r="Q150" s="19">
+        <v>0</v>
+      </c>
       <c r="R150" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S150" s="19">
         <v>80</v>
       </c>
       <c r="T150" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U150" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V150" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W150" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="X150" s="19">
         <f t="shared" si="83"/>
@@ -21558,7 +21942,7 @@
       </c>
       <c r="Y150" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z150" s="19">
         <f t="shared" si="85"/>
@@ -21566,7 +21950,7 @@
       </c>
       <c r="AA150" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB150" s="9">
         <v>39.270000000000003</v>
@@ -21579,55 +21963,89 @@
       </c>
       <c r="AE150" s="10">
         <f t="shared" si="91"/>
-        <v>5811.2</v>
+        <v>7750.7749999999996</v>
       </c>
       <c r="AF150" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG150" s="11">
         <f t="shared" si="86"/>
-        <v>377.72800000000001</v>
+        <v>503.80037499999997</v>
       </c>
       <c r="AH150" s="80">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>27.489000000000004</v>
       </c>
       <c r="AI150" s="10">
         <f t="shared" si="93"/>
-        <v>5433.4719999999998</v>
+        <v>7246.9746249999998</v>
       </c>
       <c r="AJ150" s="5">
         <v>0.18</v>
       </c>
       <c r="AK150" s="12">
         <f t="shared" si="94"/>
-        <v>978.02495999999996</v>
+        <v>1304.4554324999999</v>
       </c>
       <c r="AL150" s="10">
         <f t="shared" si="95"/>
-        <v>6411.4969599999995</v>
+        <v>8551.4300574999997</v>
       </c>
       <c r="AP150" s="13"/>
     </row>
     <row r="151" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A151" s="18"/>
-      <c r="C151" s="19"/>
-      <c r="E151" s="6"/>
-      <c r="F151" s="20"/>
-      <c r="G151" s="20"/>
-      <c r="H151" s="20"/>
-      <c r="I151" s="6"/>
-      <c r="J151" s="70"/>
-      <c r="K151" s="21"/>
-      <c r="L151" s="21"/>
-      <c r="M151" s="21"/>
+      <c r="A151" s="18">
+        <v>46189</v>
+      </c>
+      <c r="B151" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C151" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D151" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E151" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F151" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G151" s="20" t="s">
+        <v>272</v>
+      </c>
+      <c r="H151" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="I151" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="J151" s="70">
+        <v>14</v>
+      </c>
+      <c r="K151" s="21">
+        <v>10</v>
+      </c>
+      <c r="L151" s="21">
+        <v>10</v>
+      </c>
+      <c r="M151" s="21">
+        <v>2</v>
+      </c>
       <c r="N151" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O151" s="19"/>
-      <c r="P151" s="19"/>
-      <c r="Q151" s="21"/>
+        <v>22</v>
+      </c>
+      <c r="O151" s="19">
+        <v>0</v>
+      </c>
+      <c r="P151" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q151" s="21">
+        <v>0</v>
+      </c>
       <c r="R151" s="9">
         <f t="shared" si="79"/>
         <v>0</v>
@@ -21637,19 +22055,19 @@
       </c>
       <c r="T151" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U151" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V151" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W151" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="X151" s="19">
         <f t="shared" si="83"/>
@@ -21678,93 +22096,127 @@
       </c>
       <c r="AE151" s="10">
         <f t="shared" si="91"/>
-        <v>2905.6</v>
+        <v>4609.5550000000003</v>
       </c>
       <c r="AF151" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG151" s="11">
         <f t="shared" si="86"/>
-        <v>188.864</v>
+        <v>299.62107500000002</v>
       </c>
       <c r="AH151" s="80">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>19.242300000000004</v>
       </c>
       <c r="AI151" s="10">
         <f t="shared" si="93"/>
-        <v>2716.7359999999999</v>
+        <v>4309.9339250000003</v>
       </c>
       <c r="AJ151" s="5">
         <v>0.18</v>
       </c>
       <c r="AK151" s="12">
         <f t="shared" si="94"/>
-        <v>489.01247999999998</v>
+        <v>775.78810650000003</v>
       </c>
       <c r="AL151" s="10">
         <f t="shared" si="95"/>
-        <v>3205.7484799999997</v>
+        <v>5085.7220315000004</v>
       </c>
       <c r="AP151" s="13"/>
     </row>
     <row r="152" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A152" s="18"/>
-      <c r="C152" s="19"/>
-      <c r="E152" s="6"/>
-      <c r="F152" s="20"/>
-      <c r="G152" s="20"/>
-      <c r="H152" s="20"/>
-      <c r="I152" s="6"/>
-      <c r="J152" s="70"/>
-      <c r="K152" s="19"/>
-      <c r="L152" s="19"/>
-      <c r="M152" s="19"/>
+      <c r="A152" s="18">
+        <v>46189</v>
+      </c>
+      <c r="B152" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C152" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D152" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E152" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F152" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G152" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="H152" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="I152" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="J152" s="70">
+        <v>20</v>
+      </c>
+      <c r="K152" s="19">
+        <v>40</v>
+      </c>
+      <c r="L152" s="19">
+        <v>40</v>
+      </c>
+      <c r="M152" s="19">
+        <v>20</v>
+      </c>
       <c r="N152" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O152" s="19"/>
-      <c r="P152" s="19"/>
-      <c r="Q152" s="19"/>
+        <v>100</v>
+      </c>
+      <c r="O152" s="19">
+        <v>80</v>
+      </c>
+      <c r="P152" s="19">
+        <v>30</v>
+      </c>
+      <c r="Q152" s="19">
+        <v>40</v>
+      </c>
       <c r="R152" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="S152" s="19">
         <v>80</v>
       </c>
       <c r="T152" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U152" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V152" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W152" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X152" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y152" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z152" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA152" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AB152" s="9">
         <v>39.270000000000003</v>
@@ -21777,93 +22229,127 @@
       </c>
       <c r="AE152" s="10">
         <f t="shared" si="91"/>
-        <v>5811.2</v>
+        <v>11842.849999999999</v>
       </c>
       <c r="AF152" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG152" s="11">
         <f t="shared" si="86"/>
-        <v>377.72800000000001</v>
+        <v>769.78524999999991</v>
       </c>
       <c r="AH152" s="80">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>27.489000000000004</v>
       </c>
       <c r="AI152" s="10">
         <f t="shared" si="93"/>
-        <v>5433.4719999999998</v>
+        <v>11073.064749999998</v>
       </c>
       <c r="AJ152" s="5">
         <v>0.18</v>
       </c>
       <c r="AK152" s="12">
         <f t="shared" si="94"/>
-        <v>978.02495999999996</v>
+        <v>1993.1516549999994</v>
       </c>
       <c r="AL152" s="10">
         <f t="shared" si="95"/>
-        <v>6411.4969599999995</v>
+        <v>13066.216404999997</v>
       </c>
       <c r="AP152" s="13"/>
     </row>
     <row r="153" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A153" s="18"/>
-      <c r="C153" s="19"/>
-      <c r="E153" s="6"/>
-      <c r="F153" s="20"/>
-      <c r="G153" s="20"/>
-      <c r="H153" s="20"/>
-      <c r="I153" s="6"/>
-      <c r="J153" s="70"/>
-      <c r="K153" s="19"/>
-      <c r="L153" s="21"/>
-      <c r="M153" s="21"/>
+      <c r="A153" s="18">
+        <v>46189</v>
+      </c>
+      <c r="B153" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C153" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D153" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E153" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F153" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G153" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="H153" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="I153" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="J153" s="70">
+        <v>10</v>
+      </c>
+      <c r="K153" s="19">
+        <v>40</v>
+      </c>
+      <c r="L153" s="21">
+        <v>20</v>
+      </c>
+      <c r="M153" s="21">
+        <v>40</v>
+      </c>
       <c r="N153" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O153" s="19"/>
-      <c r="P153" s="19"/>
-      <c r="Q153" s="19"/>
+        <v>100</v>
+      </c>
+      <c r="O153" s="19">
+        <v>40</v>
+      </c>
+      <c r="P153" s="19">
+        <v>20</v>
+      </c>
+      <c r="Q153" s="19">
+        <v>80</v>
+      </c>
       <c r="R153" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="S153" s="19">
         <v>240</v>
       </c>
       <c r="T153" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U153" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V153" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W153" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X153" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y153" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z153" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA153" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AB153" s="9">
         <v>39.270000000000003</v>
@@ -21876,93 +22362,127 @@
       </c>
       <c r="AE153" s="10">
         <f t="shared" si="91"/>
-        <v>17433.599999999999</v>
+        <v>23072.55</v>
       </c>
       <c r="AF153" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG153" s="11">
         <f t="shared" si="86"/>
-        <v>1133.184</v>
+        <v>1499.7157500000001</v>
       </c>
       <c r="AH153" s="80">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI153" s="10">
         <f t="shared" si="93"/>
-        <v>16300.415999999999</v>
+        <v>21572.83425</v>
       </c>
       <c r="AJ153" s="5">
         <v>0.18</v>
       </c>
       <c r="AK153" s="12">
         <f t="shared" si="94"/>
-        <v>2934.0748799999997</v>
+        <v>3883.1101650000001</v>
       </c>
       <c r="AL153" s="10">
         <f t="shared" si="95"/>
-        <v>19234.490879999998</v>
+        <v>25455.944414999998</v>
       </c>
       <c r="AP153" s="13"/>
     </row>
     <row r="154" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A154" s="18"/>
-      <c r="C154" s="19"/>
-      <c r="E154" s="6"/>
-      <c r="F154" s="20"/>
-      <c r="G154" s="20"/>
-      <c r="H154" s="20"/>
-      <c r="I154" s="6"/>
-      <c r="J154" s="70"/>
-      <c r="K154" s="21"/>
-      <c r="L154" s="21"/>
-      <c r="M154" s="21"/>
+      <c r="A154" s="18">
+        <v>46189</v>
+      </c>
+      <c r="B154" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C154" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D154" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E154" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F154" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G154" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="H154" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="I154" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="J154" s="70">
+        <v>30</v>
+      </c>
+      <c r="K154" s="21">
+        <v>40</v>
+      </c>
+      <c r="L154" s="21">
+        <v>40</v>
+      </c>
+      <c r="M154" s="21">
+        <v>20</v>
+      </c>
       <c r="N154" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O154" s="19"/>
-      <c r="P154" s="21"/>
-      <c r="Q154" s="21"/>
+        <v>100</v>
+      </c>
+      <c r="O154" s="19">
+        <v>30</v>
+      </c>
+      <c r="P154" s="21">
+        <v>40</v>
+      </c>
+      <c r="Q154" s="21">
+        <v>40</v>
+      </c>
       <c r="R154" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="S154" s="19">
         <v>10</v>
       </c>
       <c r="T154" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U154" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V154" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W154" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X154" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y154" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z154" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA154" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AB154" s="9">
         <v>39.270000000000003</v>
@@ -21975,93 +22495,127 @@
       </c>
       <c r="AE154" s="10">
         <f t="shared" si="91"/>
-        <v>726.4</v>
+        <v>7150.75</v>
       </c>
       <c r="AF154" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG154" s="11">
         <f t="shared" si="86"/>
-        <v>47.216000000000001</v>
+        <v>464.79875000000004</v>
       </c>
       <c r="AH154" s="80">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>41.233500000000006</v>
       </c>
       <c r="AI154" s="10">
         <f t="shared" si="93"/>
-        <v>679.18399999999997</v>
+        <v>6685.9512500000001</v>
       </c>
       <c r="AJ154" s="5">
         <v>0.18</v>
       </c>
       <c r="AK154" s="12">
         <f t="shared" si="94"/>
-        <v>122.25312</v>
+        <v>1203.471225</v>
       </c>
       <c r="AL154" s="10">
         <f t="shared" si="95"/>
-        <v>801.43711999999994</v>
+        <v>7889.4224750000003</v>
       </c>
       <c r="AP154" s="13"/>
     </row>
     <row r="155" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A155" s="18"/>
-      <c r="C155" s="19"/>
-      <c r="E155" s="6"/>
-      <c r="F155" s="20"/>
-      <c r="G155" s="20"/>
-      <c r="H155" s="20"/>
-      <c r="I155" s="6"/>
-      <c r="J155" s="70"/>
-      <c r="K155" s="19"/>
-      <c r="L155" s="21"/>
-      <c r="M155" s="19"/>
+      <c r="A155" s="18">
+        <v>46189</v>
+      </c>
+      <c r="B155" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C155" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D155" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E155" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F155" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G155" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="H155" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="I155" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="J155" s="70">
+        <v>20</v>
+      </c>
+      <c r="K155" s="19">
+        <v>20</v>
+      </c>
+      <c r="L155" s="21">
+        <v>40</v>
+      </c>
+      <c r="M155" s="19">
+        <v>20</v>
+      </c>
       <c r="N155" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O155" s="19"/>
-      <c r="P155" s="19"/>
-      <c r="Q155" s="21"/>
+        <v>80</v>
+      </c>
+      <c r="O155" s="19">
+        <v>20</v>
+      </c>
+      <c r="P155" s="19">
+        <v>40</v>
+      </c>
+      <c r="Q155" s="21">
+        <v>80</v>
+      </c>
       <c r="R155" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="S155" s="19">
         <v>141</v>
       </c>
       <c r="T155" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U155" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V155" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W155" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X155" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y155" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z155" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA155" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AB155" s="9">
         <v>39.270000000000003</v>
@@ -22074,93 +22628,127 @@
       </c>
       <c r="AE155" s="10">
         <f t="shared" si="91"/>
-        <v>10242.24</v>
+        <v>15224.64</v>
       </c>
       <c r="AF155" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG155" s="11">
         <f t="shared" si="86"/>
-        <v>665.74559999999997</v>
+        <v>989.60159999999996</v>
       </c>
       <c r="AH155" s="80">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>27.489000000000004</v>
       </c>
       <c r="AI155" s="10">
         <f t="shared" si="93"/>
-        <v>9576.4943999999996</v>
+        <v>14235.038399999999</v>
       </c>
       <c r="AJ155" s="5">
         <v>0.18</v>
       </c>
       <c r="AK155" s="12">
         <f t="shared" si="94"/>
-        <v>1723.7689919999998</v>
+        <v>2562.306912</v>
       </c>
       <c r="AL155" s="10">
         <f t="shared" si="95"/>
-        <v>11300.263391999999</v>
+        <v>16797.345311999998</v>
       </c>
       <c r="AP155" s="13"/>
     </row>
     <row r="156" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A156" s="18"/>
-      <c r="C156" s="19"/>
-      <c r="E156" s="6"/>
-      <c r="F156" s="20"/>
-      <c r="G156" s="20"/>
-      <c r="H156" s="20"/>
-      <c r="I156" s="6"/>
-      <c r="J156" s="70"/>
-      <c r="K156" s="21"/>
-      <c r="L156" s="21"/>
-      <c r="M156" s="21"/>
+      <c r="A156" s="18">
+        <v>46189</v>
+      </c>
+      <c r="B156" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C156" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D156" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F156" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G156" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="H156" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="I156" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="J156" s="70">
+        <v>20</v>
+      </c>
+      <c r="K156" s="21">
+        <v>20</v>
+      </c>
+      <c r="L156" s="21">
+        <v>60</v>
+      </c>
+      <c r="M156" s="21">
+        <v>20</v>
+      </c>
       <c r="N156" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O156" s="19"/>
-      <c r="P156" s="19"/>
-      <c r="Q156" s="19"/>
+        <v>100</v>
+      </c>
+      <c r="O156" s="19">
+        <v>40</v>
+      </c>
+      <c r="P156" s="19">
+        <v>40</v>
+      </c>
+      <c r="Q156" s="19">
+        <v>120</v>
+      </c>
       <c r="R156" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S156" s="19">
         <v>120</v>
       </c>
       <c r="T156" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U156" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V156" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W156" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X156" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y156" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z156" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA156" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AB156" s="9">
         <v>39.270000000000003</v>
@@ -22173,93 +22761,127 @@
       </c>
       <c r="AE156" s="10">
         <f t="shared" si="91"/>
-        <v>8716.7999999999993</v>
+        <v>14748.449999999999</v>
       </c>
       <c r="AF156" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG156" s="11">
         <f t="shared" si="86"/>
-        <v>566.59199999999998</v>
+        <v>958.64924999999994</v>
       </c>
       <c r="AH156" s="80">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>27.489000000000004</v>
       </c>
       <c r="AI156" s="10">
         <f t="shared" si="93"/>
-        <v>8150.2079999999996</v>
+        <v>13789.800749999999</v>
       </c>
       <c r="AJ156" s="5">
         <v>0.18</v>
       </c>
       <c r="AK156" s="12">
         <f t="shared" si="94"/>
-        <v>1467.0374399999998</v>
+        <v>2482.1641349999995</v>
       </c>
       <c r="AL156" s="10">
         <f t="shared" si="95"/>
-        <v>9617.2454399999988</v>
+        <v>16271.964884999998</v>
       </c>
       <c r="AP156" s="13"/>
     </row>
     <row r="157" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A157" s="18"/>
-      <c r="C157" s="19"/>
-      <c r="E157" s="6"/>
-      <c r="F157" s="20"/>
-      <c r="G157" s="20"/>
-      <c r="H157" s="20"/>
-      <c r="I157" s="6"/>
-      <c r="J157" s="70"/>
-      <c r="K157" s="21"/>
-      <c r="L157" s="21"/>
-      <c r="M157" s="21"/>
+      <c r="A157" s="18">
+        <v>46189</v>
+      </c>
+      <c r="B157" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C157" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D157" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E157" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F157" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G157" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="H157" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="I157" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="J157" s="70">
+        <v>10</v>
+      </c>
+      <c r="K157" s="21">
+        <v>40</v>
+      </c>
+      <c r="L157" s="21">
+        <v>20</v>
+      </c>
+      <c r="M157" s="21">
+        <v>20</v>
+      </c>
       <c r="N157" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O157" s="19"/>
-      <c r="P157" s="19"/>
-      <c r="Q157" s="21"/>
+        <v>80</v>
+      </c>
+      <c r="O157" s="19">
+        <v>40</v>
+      </c>
+      <c r="P157" s="19">
+        <v>40</v>
+      </c>
+      <c r="Q157" s="21">
+        <v>40</v>
+      </c>
       <c r="R157" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S157" s="19">
         <v>80</v>
       </c>
       <c r="T157" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U157" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V157" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W157" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X157" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y157" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z157" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA157" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB157" s="9">
         <v>39.270000000000003</v>
@@ -22272,93 +22894,127 @@
       </c>
       <c r="AE157" s="10">
         <f t="shared" si="91"/>
-        <v>5811.2</v>
+        <v>10400.9</v>
       </c>
       <c r="AF157" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG157" s="11">
         <f t="shared" si="86"/>
-        <v>377.72800000000001</v>
+        <v>676.05849999999998</v>
       </c>
       <c r="AH157" s="80">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI157" s="10">
         <f t="shared" si="93"/>
-        <v>5433.4719999999998</v>
+        <v>9724.8415000000005</v>
       </c>
       <c r="AJ157" s="5">
         <v>0.18</v>
       </c>
       <c r="AK157" s="12">
         <f t="shared" si="94"/>
-        <v>978.02495999999996</v>
+        <v>1750.47147</v>
       </c>
       <c r="AL157" s="10">
         <f t="shared" si="95"/>
-        <v>6411.4969599999995</v>
+        <v>11475.312970000001</v>
       </c>
       <c r="AP157" s="13"/>
     </row>
     <row r="158" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A158" s="18"/>
-      <c r="C158" s="19"/>
-      <c r="E158" s="6"/>
-      <c r="F158" s="20"/>
-      <c r="G158" s="20"/>
-      <c r="H158" s="20"/>
-      <c r="I158" s="6"/>
-      <c r="J158" s="70"/>
-      <c r="K158" s="19"/>
-      <c r="L158" s="19"/>
-      <c r="M158" s="19"/>
+      <c r="A158" s="18">
+        <v>46189</v>
+      </c>
+      <c r="B158" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C158" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D158" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E158" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F158" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G158" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H158" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="I158" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="J158" s="70">
+        <v>10</v>
+      </c>
+      <c r="K158" s="19">
+        <v>20</v>
+      </c>
+      <c r="L158" s="19">
+        <v>20</v>
+      </c>
+      <c r="M158" s="19">
+        <v>20</v>
+      </c>
       <c r="N158" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O158" s="19"/>
-      <c r="P158" s="19"/>
-      <c r="Q158" s="19"/>
+        <v>60</v>
+      </c>
+      <c r="O158" s="19">
+        <v>45</v>
+      </c>
+      <c r="P158" s="19">
+        <v>40</v>
+      </c>
+      <c r="Q158" s="19">
+        <v>15</v>
+      </c>
       <c r="R158" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S158" s="19">
         <v>80</v>
       </c>
       <c r="T158" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U158" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V158" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W158" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X158" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y158" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z158" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA158" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB158" s="9">
         <v>39.270000000000003</v>
@@ -22371,93 +23027,127 @@
       </c>
       <c r="AE158" s="10">
         <f t="shared" si="91"/>
-        <v>5811.2</v>
+        <v>9351.65</v>
       </c>
       <c r="AF158" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG158" s="11">
         <f t="shared" si="86"/>
-        <v>377.72800000000001</v>
+        <v>607.85725000000002</v>
       </c>
       <c r="AH158" s="80">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI158" s="10">
         <f t="shared" si="93"/>
-        <v>5433.4719999999998</v>
+        <v>8743.7927500000005</v>
       </c>
       <c r="AJ158" s="5">
         <v>0.18</v>
       </c>
       <c r="AK158" s="12">
         <f t="shared" si="94"/>
-        <v>978.02495999999996</v>
+        <v>1573.882695</v>
       </c>
       <c r="AL158" s="10">
         <f t="shared" si="95"/>
-        <v>6411.4969599999995</v>
+        <v>10317.675445000001</v>
       </c>
       <c r="AP158" s="13"/>
     </row>
     <row r="159" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A159" s="18"/>
-      <c r="C159" s="19"/>
-      <c r="E159" s="6"/>
-      <c r="F159" s="20"/>
-      <c r="G159" s="20"/>
-      <c r="H159" s="20"/>
-      <c r="I159" s="6"/>
-      <c r="J159" s="70"/>
-      <c r="K159" s="19"/>
-      <c r="L159" s="21"/>
-      <c r="M159" s="19"/>
+      <c r="A159" s="18">
+        <v>46190</v>
+      </c>
+      <c r="B159" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C159" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D159" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E159" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F159" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G159" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="H159" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="I159" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="J159" s="70">
+        <v>12</v>
+      </c>
+      <c r="K159" s="19">
+        <v>40</v>
+      </c>
+      <c r="L159" s="21">
+        <v>30</v>
+      </c>
+      <c r="M159" s="19">
+        <v>20</v>
+      </c>
       <c r="N159" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O159" s="19"/>
-      <c r="P159" s="21"/>
-      <c r="Q159" s="19"/>
+        <v>90</v>
+      </c>
+      <c r="O159" s="19">
+        <v>6</v>
+      </c>
+      <c r="P159" s="21">
+        <v>5</v>
+      </c>
+      <c r="Q159" s="19">
+        <v>4</v>
+      </c>
       <c r="R159" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S159" s="19">
         <v>40</v>
       </c>
       <c r="T159" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U159" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V159" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W159" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X159" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Y159" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Z159" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AA159" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB159" s="9">
         <v>39.270000000000003</v>
@@ -22470,81 +23160,115 @@
       </c>
       <c r="AE159" s="10">
         <f t="shared" si="91"/>
-        <v>2905.6</v>
+        <v>8098.4650000000001</v>
       </c>
       <c r="AF159" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG159" s="11">
         <f t="shared" si="86"/>
-        <v>188.864</v>
+        <v>526.40022499999998</v>
       </c>
       <c r="AH159" s="80">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>16.493400000000001</v>
       </c>
       <c r="AI159" s="10">
         <f t="shared" si="93"/>
-        <v>2716.7359999999999</v>
+        <v>7572.0647749999998</v>
       </c>
       <c r="AJ159" s="5">
         <v>0.18</v>
       </c>
       <c r="AK159" s="12">
         <f t="shared" si="94"/>
-        <v>489.01247999999998</v>
+        <v>1362.9716595</v>
       </c>
       <c r="AL159" s="10">
         <f t="shared" si="95"/>
-        <v>3205.7484799999997</v>
+        <v>8935.0364344999998</v>
       </c>
       <c r="AP159" s="13"/>
     </row>
     <row r="160" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A160" s="18"/>
-      <c r="C160" s="19"/>
-      <c r="E160" s="6"/>
-      <c r="F160" s="20"/>
-      <c r="G160" s="20"/>
-      <c r="H160" s="20"/>
-      <c r="I160" s="6"/>
-      <c r="J160" s="70"/>
-      <c r="K160" s="19"/>
-      <c r="L160" s="19"/>
-      <c r="M160" s="19"/>
+      <c r="A160" s="18">
+        <v>46190</v>
+      </c>
+      <c r="B160" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C160" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D160" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E160" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F160" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G160" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="H160" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="I160" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="J160" s="70">
+        <v>12</v>
+      </c>
+      <c r="K160" s="19">
+        <v>26</v>
+      </c>
+      <c r="L160" s="19">
+        <v>36</v>
+      </c>
+      <c r="M160" s="19">
+        <v>20</v>
+      </c>
       <c r="N160" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O160" s="19"/>
-      <c r="P160" s="19"/>
-      <c r="Q160" s="19"/>
+        <v>82</v>
+      </c>
+      <c r="O160" s="19">
+        <v>2</v>
+      </c>
+      <c r="P160" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q160" s="19">
+        <v>3</v>
+      </c>
       <c r="R160" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S160" s="19">
         <v>41</v>
       </c>
       <c r="T160" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U160" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V160" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W160" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="X160" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Y160" s="19">
         <f t="shared" si="84"/>
@@ -22552,11 +23276,11 @@
       </c>
       <c r="Z160" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AA160" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AB160" s="9">
         <v>39.270000000000003</v>
@@ -22569,58 +23293,90 @@
       </c>
       <c r="AE160" s="10">
         <f t="shared" si="91"/>
-        <v>2978.2400000000002</v>
+        <v>7751.4050000000007</v>
       </c>
       <c r="AF160" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG160" s="11">
         <f t="shared" si="86"/>
-        <v>193.58560000000003</v>
+        <v>503.84132500000004</v>
       </c>
       <c r="AH160" s="80">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>16.493400000000001</v>
       </c>
       <c r="AI160" s="10">
         <f t="shared" si="93"/>
-        <v>2784.6544000000004</v>
+        <v>7247.5636750000003</v>
       </c>
       <c r="AJ160" s="5">
         <v>0.18</v>
       </c>
       <c r="AK160" s="12">
         <f t="shared" si="94"/>
-        <v>501.23779200000007</v>
+        <v>1304.5614615</v>
       </c>
       <c r="AL160" s="10">
         <f t="shared" si="95"/>
-        <v>3285.8921920000003</v>
+        <v>8552.1251365000007</v>
       </c>
       <c r="AP160" s="13"/>
     </row>
     <row r="161" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A161" s="18"/>
-      <c r="C161" s="19"/>
-      <c r="E161" s="6"/>
-      <c r="F161" s="20"/>
-      <c r="G161" s="20"/>
-      <c r="H161" s="20"/>
-      <c r="I161" s="6"/>
+      <c r="A161" s="18">
+        <v>46190</v>
+      </c>
+      <c r="B161" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C161" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D161" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E161" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F161" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G161" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="H161" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="I161" s="6" t="s">
+        <v>289</v>
+      </c>
       <c r="J161" s="70"/>
-      <c r="K161" s="19"/>
-      <c r="L161" s="21"/>
-      <c r="M161" s="21"/>
+      <c r="K161" s="19">
+        <v>0</v>
+      </c>
+      <c r="L161" s="21">
+        <v>4</v>
+      </c>
+      <c r="M161" s="21">
+        <v>4</v>
+      </c>
       <c r="N161" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O161" s="19"/>
-      <c r="P161" s="21"/>
-      <c r="Q161" s="21"/>
+        <v>8</v>
+      </c>
+      <c r="O161" s="19">
+        <v>5</v>
+      </c>
+      <c r="P161" s="21">
+        <v>10</v>
+      </c>
+      <c r="Q161" s="21">
+        <v>40</v>
+      </c>
       <c r="R161" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="S161" s="19">
         <v>20</v>
@@ -22631,31 +23387,31 @@
       </c>
       <c r="U161" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="V161" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W161" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="X161" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Y161" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z161" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA161" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB161" s="9">
         <v>39.270000000000003</v>
@@ -22668,14 +23424,14 @@
       </c>
       <c r="AE161" s="10">
         <f t="shared" si="91"/>
-        <v>1452.8</v>
+        <v>1872.5</v>
       </c>
       <c r="AF161" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG161" s="11">
         <f t="shared" si="86"/>
-        <v>94.432000000000002</v>
+        <v>121.71250000000001</v>
       </c>
       <c r="AH161" s="80">
         <f t="shared" si="92"/>
@@ -22683,78 +23439,110 @@
       </c>
       <c r="AI161" s="10">
         <f t="shared" si="93"/>
-        <v>1358.3679999999999</v>
+        <v>1750.7874999999999</v>
       </c>
       <c r="AJ161" s="5">
         <v>0.18</v>
       </c>
       <c r="AK161" s="12">
         <f t="shared" si="94"/>
-        <v>244.50623999999999</v>
+        <v>315.14174999999994</v>
       </c>
       <c r="AL161" s="10">
         <f t="shared" si="95"/>
-        <v>1602.8742399999999</v>
+        <v>2065.9292499999997</v>
       </c>
       <c r="AP161" s="13"/>
     </row>
     <row r="162" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A162" s="18"/>
-      <c r="C162" s="19"/>
-      <c r="E162" s="6"/>
-      <c r="F162" s="20"/>
-      <c r="G162" s="20"/>
-      <c r="H162" s="20"/>
-      <c r="I162" s="6"/>
+      <c r="A162" s="18">
+        <v>46190</v>
+      </c>
+      <c r="B162" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C162" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D162" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E162" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F162" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G162" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="H162" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="I162" s="6" t="s">
+        <v>289</v>
+      </c>
       <c r="J162" s="70"/>
-      <c r="K162" s="19"/>
-      <c r="L162" s="19"/>
-      <c r="M162" s="21"/>
+      <c r="K162" s="19">
+        <v>6</v>
+      </c>
+      <c r="L162" s="19">
+        <v>4</v>
+      </c>
+      <c r="M162" s="21">
+        <v>4</v>
+      </c>
       <c r="N162" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O162" s="19"/>
-      <c r="P162" s="19"/>
-      <c r="Q162" s="21"/>
+        <v>14</v>
+      </c>
+      <c r="O162" s="19">
+        <v>5</v>
+      </c>
+      <c r="P162" s="19">
+        <v>7</v>
+      </c>
+      <c r="Q162" s="21">
+        <v>20</v>
+      </c>
       <c r="R162" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="S162" s="19">
         <v>40</v>
       </c>
       <c r="T162" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="U162" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="V162" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W162" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X162" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Y162" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="Z162" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA162" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB162" s="9">
         <v>39.270000000000003</v>
@@ -22767,14 +23555,14 @@
       </c>
       <c r="AE162" s="10">
         <f t="shared" si="91"/>
-        <v>2905.6</v>
+        <v>3640.0749999999998</v>
       </c>
       <c r="AF162" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG162" s="11">
         <f t="shared" si="86"/>
-        <v>188.864</v>
+        <v>236.60487499999999</v>
       </c>
       <c r="AH162" s="80">
         <f t="shared" si="92"/>
@@ -22782,78 +23570,110 @@
       </c>
       <c r="AI162" s="10">
         <f t="shared" si="93"/>
-        <v>2716.7359999999999</v>
+        <v>3403.4701249999998</v>
       </c>
       <c r="AJ162" s="5">
         <v>0.18</v>
       </c>
       <c r="AK162" s="12">
         <f t="shared" si="94"/>
-        <v>489.01247999999998</v>
+        <v>612.62462249999999</v>
       </c>
       <c r="AL162" s="10">
         <f t="shared" si="95"/>
-        <v>3205.7484799999997</v>
+        <v>4016.0947474999998</v>
       </c>
       <c r="AP162" s="13"/>
     </row>
     <row r="163" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A163" s="18"/>
-      <c r="C163" s="19"/>
-      <c r="E163" s="6"/>
-      <c r="F163" s="20"/>
-      <c r="G163" s="20"/>
-      <c r="H163" s="20"/>
-      <c r="I163" s="6"/>
+      <c r="A163" s="18">
+        <v>46190</v>
+      </c>
+      <c r="B163" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C163" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D163" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E163" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F163" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G163" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="H163" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="I163" s="6" t="s">
+        <v>289</v>
+      </c>
       <c r="J163" s="70"/>
-      <c r="K163" s="21"/>
-      <c r="L163" s="19"/>
-      <c r="M163" s="21"/>
+      <c r="K163" s="21">
+        <v>6</v>
+      </c>
+      <c r="L163" s="19">
+        <v>4</v>
+      </c>
+      <c r="M163" s="21">
+        <v>4</v>
+      </c>
       <c r="N163" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O163" s="19"/>
-      <c r="P163" s="19"/>
-      <c r="Q163" s="19"/>
+        <v>14</v>
+      </c>
+      <c r="O163" s="19">
+        <v>4</v>
+      </c>
+      <c r="P163" s="19">
+        <v>10</v>
+      </c>
+      <c r="Q163" s="19">
+        <v>14</v>
+      </c>
       <c r="R163" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S163" s="19">
         <v>40</v>
       </c>
       <c r="T163" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="U163" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="V163" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W163" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X163" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Y163" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z163" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA163" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB163" s="9">
         <v>39.270000000000003</v>
@@ -22866,14 +23686,14 @@
       </c>
       <c r="AE163" s="10">
         <f t="shared" si="91"/>
-        <v>2905.6</v>
+        <v>3640.0749999999998</v>
       </c>
       <c r="AF163" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG163" s="11">
         <f t="shared" si="86"/>
-        <v>188.864</v>
+        <v>236.60487499999999</v>
       </c>
       <c r="AH163" s="80">
         <f t="shared" si="92"/>
@@ -22881,78 +23701,112 @@
       </c>
       <c r="AI163" s="10">
         <f t="shared" si="93"/>
-        <v>2716.7359999999999</v>
+        <v>3403.4701249999998</v>
       </c>
       <c r="AJ163" s="5">
         <v>0.18</v>
       </c>
       <c r="AK163" s="12">
         <f t="shared" si="94"/>
-        <v>489.01247999999998</v>
+        <v>612.62462249999999</v>
       </c>
       <c r="AL163" s="10">
         <f t="shared" si="95"/>
-        <v>3205.7484799999997</v>
+        <v>4016.0947474999998</v>
       </c>
       <c r="AP163" s="13"/>
     </row>
     <row r="164" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A164" s="18"/>
-      <c r="C164" s="19"/>
-      <c r="E164" s="6"/>
-      <c r="F164" s="20"/>
-      <c r="G164" s="20"/>
-      <c r="H164" s="20"/>
-      <c r="I164" s="6"/>
-      <c r="J164" s="70"/>
-      <c r="K164" s="19"/>
-      <c r="L164" s="19"/>
-      <c r="M164" s="19"/>
+      <c r="A164" s="18">
+        <v>46190</v>
+      </c>
+      <c r="B164" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C164" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D164" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E164" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F164" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G164" s="20" t="s">
+        <v>290</v>
+      </c>
+      <c r="H164" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="I164" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="J164" s="70">
+        <v>10</v>
+      </c>
+      <c r="K164" s="19">
+        <v>20</v>
+      </c>
+      <c r="L164" s="19">
+        <v>10</v>
+      </c>
+      <c r="M164" s="19">
+        <v>5</v>
+      </c>
       <c r="N164" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O164" s="19"/>
-      <c r="P164" s="19"/>
-      <c r="Q164" s="19"/>
+        <v>35</v>
+      </c>
+      <c r="O164" s="19">
+        <v>40</v>
+      </c>
+      <c r="P164" s="19">
+        <v>20</v>
+      </c>
+      <c r="Q164" s="19">
+        <v>20</v>
+      </c>
       <c r="R164" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S164" s="19">
         <v>80</v>
       </c>
       <c r="T164" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U164" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V164" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W164" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X164" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y164" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z164" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA164" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AB164" s="9">
         <v>39.270000000000003</v>
@@ -22965,93 +23819,127 @@
       </c>
       <c r="AE164" s="10">
         <f t="shared" si="91"/>
-        <v>5811.2</v>
+        <v>8040.0874999999996</v>
       </c>
       <c r="AF164" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG164" s="11">
         <f t="shared" si="86"/>
-        <v>377.72800000000001</v>
+        <v>522.60568750000004</v>
       </c>
       <c r="AH164" s="80">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI164" s="10">
         <f t="shared" si="93"/>
-        <v>5433.4719999999998</v>
+        <v>7517.4818124999993</v>
       </c>
       <c r="AJ164" s="5">
         <v>0.18</v>
       </c>
       <c r="AK164" s="12">
         <f t="shared" si="94"/>
-        <v>978.02495999999996</v>
+        <v>1353.1467262499998</v>
       </c>
       <c r="AL164" s="10">
         <f t="shared" si="95"/>
-        <v>6411.4969599999995</v>
+        <v>8870.6285387499993</v>
       </c>
       <c r="AP164" s="13"/>
     </row>
     <row r="165" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A165" s="18"/>
-      <c r="C165" s="19"/>
-      <c r="E165" s="6"/>
-      <c r="F165" s="20"/>
-      <c r="G165" s="20"/>
-      <c r="H165" s="20"/>
-      <c r="I165" s="6"/>
-      <c r="J165" s="70"/>
-      <c r="K165" s="19"/>
-      <c r="L165" s="21"/>
-      <c r="M165" s="19"/>
+      <c r="A165" s="18">
+        <v>46190</v>
+      </c>
+      <c r="B165" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C165" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D165" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E165" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F165" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G165" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="H165" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="I165" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="J165" s="70">
+        <v>14</v>
+      </c>
+      <c r="K165" s="19">
+        <v>20</v>
+      </c>
+      <c r="L165" s="21">
+        <v>20</v>
+      </c>
+      <c r="M165" s="19">
+        <v>10</v>
+      </c>
       <c r="N165" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O165" s="19"/>
-      <c r="P165" s="19"/>
-      <c r="Q165" s="19"/>
+        <v>50</v>
+      </c>
+      <c r="O165" s="19">
+        <v>40</v>
+      </c>
+      <c r="P165" s="19">
+        <v>20</v>
+      </c>
+      <c r="Q165" s="19">
+        <v>20</v>
+      </c>
       <c r="R165" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S165" s="19">
         <v>294</v>
       </c>
       <c r="T165" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U165" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V165" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W165" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X165" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y165" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z165" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA165" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AB165" s="9">
         <v>39.270000000000003</v>
@@ -23064,93 +23952,127 @@
       </c>
       <c r="AE165" s="10">
         <f t="shared" si="91"/>
-        <v>21356.16</v>
+        <v>24529.064999999999</v>
       </c>
       <c r="AF165" s="22">
         <v>0.14000000000000001</v>
       </c>
       <c r="AG165" s="11">
         <f t="shared" si="86"/>
-        <v>2989.8624000000004</v>
+        <v>3434.0691000000002</v>
       </c>
       <c r="AH165" s="80">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>19.242300000000004</v>
       </c>
       <c r="AI165" s="10">
         <f t="shared" si="93"/>
-        <v>18366.297599999998</v>
+        <v>21094.995899999998</v>
       </c>
       <c r="AJ165" s="5">
         <v>0.18</v>
       </c>
       <c r="AK165" s="12">
         <f t="shared" si="94"/>
-        <v>3305.9335679999995</v>
+        <v>3797.0992619999997</v>
       </c>
       <c r="AL165" s="10">
         <f t="shared" si="95"/>
-        <v>21672.231167999998</v>
+        <v>24892.095161999998</v>
       </c>
       <c r="AP165" s="13"/>
     </row>
     <row r="166" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A166" s="18"/>
-      <c r="C166" s="19"/>
-      <c r="E166" s="6"/>
-      <c r="F166" s="20"/>
-      <c r="G166" s="20"/>
-      <c r="H166" s="20"/>
-      <c r="I166" s="6"/>
-      <c r="J166" s="70"/>
-      <c r="K166" s="19"/>
-      <c r="L166" s="21"/>
-      <c r="M166" s="21"/>
+      <c r="A166" s="18">
+        <v>46190</v>
+      </c>
+      <c r="B166" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C166" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D166" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E166" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F166" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G166" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="H166" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="I166" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="J166" s="70">
+        <v>40</v>
+      </c>
+      <c r="K166" s="19">
+        <v>20</v>
+      </c>
+      <c r="L166" s="21">
+        <v>20</v>
+      </c>
+      <c r="M166" s="21">
+        <v>5</v>
+      </c>
       <c r="N166" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O166" s="19"/>
-      <c r="P166" s="19"/>
-      <c r="Q166" s="19"/>
+        <v>45</v>
+      </c>
+      <c r="O166" s="19">
+        <v>10</v>
+      </c>
+      <c r="P166" s="19">
+        <v>10</v>
+      </c>
+      <c r="Q166" s="19">
+        <v>20</v>
+      </c>
       <c r="R166" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S166" s="19">
         <v>714</v>
       </c>
       <c r="T166" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U166" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V166" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W166" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="X166" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y166" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z166" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA166" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB166" s="9">
         <v>39.270000000000003</v>
@@ -23163,69 +24085,103 @@
       </c>
       <c r="AE166" s="10">
         <f t="shared" si="91"/>
-        <v>51864.959999999999</v>
+        <v>55796.572500000002</v>
       </c>
       <c r="AF166" s="22">
         <v>0.14000000000000001</v>
       </c>
       <c r="AG166" s="11">
         <f t="shared" si="86"/>
-        <v>7261.0944000000009</v>
+        <v>7811.5201500000012</v>
       </c>
       <c r="AH166" s="80">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI166" s="10">
         <f t="shared" si="93"/>
-        <v>44603.865599999997</v>
+        <v>47985.052349999998</v>
       </c>
       <c r="AJ166" s="5">
         <v>0.18</v>
       </c>
       <c r="AK166" s="12">
         <f t="shared" si="94"/>
-        <v>8028.6958079999995</v>
+        <v>8637.3094229999988</v>
       </c>
       <c r="AL166" s="10">
         <f t="shared" si="95"/>
-        <v>52632.561407999994</v>
+        <v>56622.361772999997</v>
       </c>
       <c r="AP166" s="13"/>
     </row>
     <row r="167" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A167" s="18"/>
-      <c r="C167" s="19"/>
-      <c r="E167" s="6"/>
-      <c r="F167" s="20"/>
-      <c r="G167" s="20"/>
-      <c r="H167" s="20"/>
-      <c r="I167" s="6"/>
-      <c r="J167" s="70"/>
-      <c r="K167" s="21"/>
-      <c r="L167" s="21"/>
-      <c r="M167" s="21"/>
+      <c r="A167" s="18">
+        <v>46190</v>
+      </c>
+      <c r="B167" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C167" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D167" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E167" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F167" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G167" s="20" t="s">
+        <v>293</v>
+      </c>
+      <c r="H167" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="I167" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="J167" s="70">
+        <v>80</v>
+      </c>
+      <c r="K167" s="21">
+        <v>10</v>
+      </c>
+      <c r="L167" s="21">
+        <v>20</v>
+      </c>
+      <c r="M167" s="21">
+        <v>0</v>
+      </c>
       <c r="N167" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O167" s="19"/>
-      <c r="P167" s="21"/>
-      <c r="Q167" s="19"/>
+        <v>30</v>
+      </c>
+      <c r="O167" s="19">
+        <v>5</v>
+      </c>
+      <c r="P167" s="21">
+        <v>20</v>
+      </c>
+      <c r="Q167" s="19">
+        <v>15</v>
+      </c>
       <c r="R167" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S167" s="19">
         <v>11</v>
       </c>
       <c r="T167" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U167" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V167" s="19">
         <f t="shared" si="82"/>
@@ -23233,23 +24189,23 @@
       </c>
       <c r="W167" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X167" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Y167" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z167" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA167" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB167" s="9">
         <v>39.270000000000003</v>
@@ -23262,81 +24218,109 @@
       </c>
       <c r="AE167" s="10">
         <f t="shared" si="91"/>
-        <v>799.04</v>
+        <v>5514.5150000000003</v>
       </c>
       <c r="AF167" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG167" s="11">
         <f t="shared" si="86"/>
-        <v>51.937599999999996</v>
+        <v>358.44347500000003</v>
       </c>
       <c r="AH167" s="80">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>109.95600000000002</v>
       </c>
       <c r="AI167" s="10">
         <f t="shared" si="93"/>
-        <v>747.10239999999999</v>
+        <v>5156.0715250000003</v>
       </c>
       <c r="AJ167" s="5">
         <v>0.18</v>
       </c>
       <c r="AK167" s="12">
         <f t="shared" si="94"/>
-        <v>134.478432</v>
+        <v>928.09287449999999</v>
       </c>
       <c r="AL167" s="10">
         <f t="shared" si="95"/>
-        <v>881.58083199999999</v>
+        <v>6084.1643995000004</v>
       </c>
       <c r="AP167" s="13"/>
     </row>
     <row r="168" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A168" s="18"/>
-      <c r="C168" s="19"/>
-      <c r="E168" s="6"/>
-      <c r="F168" s="20"/>
-      <c r="G168" s="20"/>
-      <c r="H168" s="20"/>
+      <c r="A168" s="18">
+        <v>46190</v>
+      </c>
+      <c r="B168" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C168" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D168" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E168" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F168" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="G168" s="20" t="s">
+        <v>295</v>
+      </c>
+      <c r="H168" s="20" t="s">
+        <v>228</v>
+      </c>
       <c r="I168" s="6"/>
       <c r="J168" s="70"/>
-      <c r="K168" s="21"/>
-      <c r="L168" s="21"/>
-      <c r="M168" s="21"/>
+      <c r="K168" s="21">
+        <v>40</v>
+      </c>
+      <c r="L168" s="21">
+        <v>40</v>
+      </c>
+      <c r="M168" s="21">
+        <v>80</v>
+      </c>
       <c r="N168" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O168" s="19"/>
+        <v>160</v>
+      </c>
+      <c r="O168" s="19">
+        <v>40</v>
+      </c>
       <c r="P168" s="19"/>
-      <c r="Q168" s="19"/>
+      <c r="Q168" s="19">
+        <v>80</v>
+      </c>
       <c r="R168" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S168" s="19">
         <v>120</v>
       </c>
       <c r="T168" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U168" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V168" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W168" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="X168" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y168" s="19">
         <f t="shared" si="84"/>
@@ -23344,11 +24328,11 @@
       </c>
       <c r="Z168" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA168" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB168" s="9">
         <v>39.270000000000003</v>
@@ -23361,14 +24345,14 @@
       </c>
       <c r="AE168" s="10">
         <f t="shared" si="91"/>
-        <v>8716.7999999999993</v>
+        <v>17110.8</v>
       </c>
       <c r="AF168" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG168" s="11">
         <f t="shared" si="86"/>
-        <v>566.59199999999998</v>
+        <v>1112.202</v>
       </c>
       <c r="AH168" s="80">
         <f t="shared" si="92"/>
@@ -23376,78 +24360,110 @@
       </c>
       <c r="AI168" s="10">
         <f t="shared" si="93"/>
-        <v>8150.2079999999996</v>
+        <v>15998.598</v>
       </c>
       <c r="AJ168" s="5">
         <v>0.18</v>
       </c>
       <c r="AK168" s="12">
         <f t="shared" si="94"/>
-        <v>1467.0374399999998</v>
+        <v>2879.74764</v>
       </c>
       <c r="AL168" s="10">
         <f t="shared" si="95"/>
-        <v>9617.2454399999988</v>
+        <v>18878.34564</v>
       </c>
       <c r="AP168" s="13"/>
     </row>
     <row r="169" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A169" s="18"/>
-      <c r="C169" s="19"/>
-      <c r="E169" s="6"/>
-      <c r="F169" s="20"/>
-      <c r="G169" s="20"/>
-      <c r="H169" s="20"/>
-      <c r="I169" s="6"/>
+      <c r="A169" s="18">
+        <v>46190</v>
+      </c>
+      <c r="B169" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C169" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D169" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E169" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F169" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="G169" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="H169" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="I169" s="6" t="s">
+        <v>323</v>
+      </c>
       <c r="J169" s="70"/>
-      <c r="K169" s="21"/>
-      <c r="L169" s="21"/>
-      <c r="M169" s="21"/>
+      <c r="K169" s="21">
+        <v>80</v>
+      </c>
+      <c r="L169" s="21">
+        <v>80</v>
+      </c>
+      <c r="M169" s="21">
+        <v>200</v>
+      </c>
       <c r="N169" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O169" s="19"/>
-      <c r="P169" s="19"/>
-      <c r="Q169" s="21"/>
+        <v>360</v>
+      </c>
+      <c r="O169" s="19">
+        <v>80</v>
+      </c>
+      <c r="P169" s="19">
+        <v>80</v>
+      </c>
+      <c r="Q169" s="21">
+        <v>200</v>
+      </c>
       <c r="R169" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="S169" s="19">
         <v>80</v>
       </c>
       <c r="T169" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U169" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V169" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="W169" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="X169" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y169" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z169" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA169" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AB169" s="9">
         <v>39.270000000000003</v>
@@ -23460,14 +24476,14 @@
       </c>
       <c r="AE169" s="10">
         <f t="shared" si="91"/>
-        <v>5811.2</v>
+        <v>24697.7</v>
       </c>
       <c r="AF169" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG169" s="11">
         <f t="shared" si="86"/>
-        <v>377.72800000000001</v>
+        <v>1605.3505</v>
       </c>
       <c r="AH169" s="80">
         <f t="shared" si="92"/>
@@ -23475,78 +24491,110 @@
       </c>
       <c r="AI169" s="10">
         <f t="shared" si="93"/>
-        <v>5433.4719999999998</v>
+        <v>23092.3495</v>
       </c>
       <c r="AJ169" s="5">
         <v>0.18</v>
       </c>
       <c r="AK169" s="12">
         <f t="shared" si="94"/>
-        <v>978.02495999999996</v>
+        <v>4156.62291</v>
       </c>
       <c r="AL169" s="10">
         <f t="shared" si="95"/>
-        <v>6411.4969599999995</v>
+        <v>27248.972410000002</v>
       </c>
       <c r="AP169" s="13"/>
     </row>
     <row r="170" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A170" s="18"/>
-      <c r="C170" s="19"/>
-      <c r="E170" s="6"/>
-      <c r="F170" s="20"/>
-      <c r="G170" s="20"/>
-      <c r="H170" s="20"/>
-      <c r="I170" s="6"/>
+      <c r="A170" s="18">
+        <v>46190</v>
+      </c>
+      <c r="B170" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C170" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D170" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E170" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F170" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="G170" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="H170" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="I170" s="6" t="s">
+        <v>324</v>
+      </c>
       <c r="J170" s="70"/>
-      <c r="K170" s="21"/>
-      <c r="L170" s="21"/>
-      <c r="M170" s="21"/>
+      <c r="K170" s="21">
+        <v>80</v>
+      </c>
+      <c r="L170" s="21">
+        <v>80</v>
+      </c>
+      <c r="M170" s="21">
+        <v>80</v>
+      </c>
       <c r="N170" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O170" s="19"/>
-      <c r="P170" s="19"/>
-      <c r="Q170" s="19"/>
+        <v>240</v>
+      </c>
+      <c r="O170" s="19">
+        <v>80</v>
+      </c>
+      <c r="P170" s="19">
+        <v>80</v>
+      </c>
+      <c r="Q170" s="19">
+        <v>80</v>
+      </c>
       <c r="R170" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="S170" s="19">
         <v>30</v>
       </c>
       <c r="T170" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U170" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V170" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W170" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X170" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y170" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z170" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA170" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB170" s="9">
         <v>39.270000000000003</v>
@@ -23559,14 +24607,14 @@
       </c>
       <c r="AE170" s="10">
         <f t="shared" si="91"/>
-        <v>2179.1999999999998</v>
+        <v>14770.2</v>
       </c>
       <c r="AF170" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG170" s="11">
         <f t="shared" si="86"/>
-        <v>141.648</v>
+        <v>960.0630000000001</v>
       </c>
       <c r="AH170" s="80">
         <f t="shared" si="92"/>
@@ -23574,78 +24622,110 @@
       </c>
       <c r="AI170" s="10">
         <f t="shared" si="93"/>
-        <v>2037.5519999999999</v>
+        <v>13810.137000000001</v>
       </c>
       <c r="AJ170" s="5">
         <v>0.18</v>
       </c>
       <c r="AK170" s="12">
         <f t="shared" si="94"/>
-        <v>366.75935999999996</v>
+        <v>2485.8246600000002</v>
       </c>
       <c r="AL170" s="10">
         <f t="shared" si="95"/>
-        <v>2404.3113599999997</v>
+        <v>16295.961660000001</v>
       </c>
       <c r="AP170" s="13"/>
     </row>
     <row r="171" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A171" s="18"/>
-      <c r="C171" s="19"/>
-      <c r="E171" s="6"/>
-      <c r="F171" s="20"/>
-      <c r="G171" s="20"/>
-      <c r="H171" s="20"/>
-      <c r="I171" s="6"/>
+      <c r="A171" s="18">
+        <v>46190</v>
+      </c>
+      <c r="B171" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C171" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D171" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E171" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F171" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="G171" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="H171" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="I171" s="6" t="s">
+        <v>322</v>
+      </c>
       <c r="J171" s="70"/>
-      <c r="K171" s="21"/>
-      <c r="L171" s="19"/>
-      <c r="M171" s="19"/>
+      <c r="K171" s="21">
+        <v>40</v>
+      </c>
+      <c r="L171" s="19">
+        <v>40</v>
+      </c>
+      <c r="M171" s="19">
+        <v>80</v>
+      </c>
       <c r="N171" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O171" s="19"/>
-      <c r="P171" s="19"/>
-      <c r="Q171" s="19"/>
+        <v>160</v>
+      </c>
+      <c r="O171" s="19">
+        <v>80</v>
+      </c>
+      <c r="P171" s="19">
+        <v>120</v>
+      </c>
+      <c r="Q171" s="19">
+        <v>40</v>
+      </c>
       <c r="R171" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="S171" s="19">
         <v>60</v>
       </c>
       <c r="T171" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U171" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V171" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W171" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="X171" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y171" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z171" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA171" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB171" s="9">
         <v>39.270000000000003</v>
@@ -23658,14 +24738,14 @@
       </c>
       <c r="AE171" s="10">
         <f t="shared" si="91"/>
-        <v>4358.3999999999996</v>
+        <v>12752.4</v>
       </c>
       <c r="AF171" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG171" s="11">
         <f t="shared" si="86"/>
-        <v>283.29599999999999</v>
+        <v>828.90599999999995</v>
       </c>
       <c r="AH171" s="80">
         <f t="shared" si="92"/>
@@ -23673,78 +24753,110 @@
       </c>
       <c r="AI171" s="10">
         <f t="shared" si="93"/>
-        <v>4075.1039999999998</v>
+        <v>11923.493999999999</v>
       </c>
       <c r="AJ171" s="5">
         <v>0.18</v>
       </c>
       <c r="AK171" s="12">
         <f t="shared" si="94"/>
-        <v>733.51871999999992</v>
+        <v>2146.2289199999996</v>
       </c>
       <c r="AL171" s="10">
         <f t="shared" si="95"/>
-        <v>4808.6227199999994</v>
+        <v>14069.722919999998</v>
       </c>
       <c r="AP171" s="13"/>
     </row>
     <row r="172" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A172" s="18"/>
-      <c r="C172" s="19"/>
-      <c r="E172" s="6"/>
-      <c r="F172" s="20"/>
-      <c r="G172" s="20"/>
-      <c r="H172" s="20"/>
-      <c r="I172" s="6"/>
+      <c r="A172" s="18">
+        <v>46190</v>
+      </c>
+      <c r="B172" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C172" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D172" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E172" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F172" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="G172" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="H172" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="I172" s="6" t="s">
+        <v>310</v>
+      </c>
       <c r="J172" s="70"/>
-      <c r="K172" s="19"/>
-      <c r="L172" s="19"/>
-      <c r="M172" s="19"/>
+      <c r="K172" s="19">
+        <v>40</v>
+      </c>
+      <c r="L172" s="19">
+        <v>40</v>
+      </c>
+      <c r="M172" s="19">
+        <v>40</v>
+      </c>
       <c r="N172" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O172" s="21"/>
-      <c r="P172" s="21"/>
-      <c r="Q172" s="21"/>
+        <v>120</v>
+      </c>
+      <c r="O172" s="21">
+        <v>40</v>
+      </c>
+      <c r="P172" s="21">
+        <v>40</v>
+      </c>
+      <c r="Q172" s="21">
+        <v>40</v>
+      </c>
       <c r="R172" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S172" s="19">
         <v>10</v>
       </c>
       <c r="T172" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U172" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V172" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W172" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="X172" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y172" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z172" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA172" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB172" s="9">
         <v>39.270000000000003</v>
@@ -23757,14 +24869,14 @@
       </c>
       <c r="AE172" s="10">
         <f t="shared" si="91"/>
-        <v>726.4</v>
+        <v>7021.9</v>
       </c>
       <c r="AF172" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG172" s="11">
         <f t="shared" si="86"/>
-        <v>47.216000000000001</v>
+        <v>456.42349999999999</v>
       </c>
       <c r="AH172" s="80">
         <f t="shared" si="92"/>
@@ -23772,78 +24884,110 @@
       </c>
       <c r="AI172" s="10">
         <f t="shared" si="93"/>
-        <v>679.18399999999997</v>
+        <v>6565.4764999999998</v>
       </c>
       <c r="AJ172" s="5">
         <v>0.18</v>
       </c>
       <c r="AK172" s="12">
         <f t="shared" si="94"/>
-        <v>122.25312</v>
+        <v>1181.78577</v>
       </c>
       <c r="AL172" s="10">
         <f t="shared" si="95"/>
-        <v>801.43711999999994</v>
+        <v>7747.2622699999993</v>
       </c>
       <c r="AP172" s="13"/>
     </row>
     <row r="173" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A173" s="18"/>
-      <c r="C173" s="19"/>
-      <c r="E173" s="6"/>
-      <c r="F173" s="20"/>
-      <c r="G173" s="20"/>
-      <c r="H173" s="20"/>
-      <c r="I173" s="6"/>
+      <c r="A173" s="18">
+        <v>46190</v>
+      </c>
+      <c r="B173" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C173" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D173" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E173" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F173" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="G173" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="H173" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="I173" s="6" t="s">
+        <v>311</v>
+      </c>
       <c r="J173" s="70"/>
-      <c r="K173" s="19"/>
-      <c r="L173" s="19"/>
-      <c r="M173" s="19"/>
+      <c r="K173" s="19">
+        <v>40</v>
+      </c>
+      <c r="L173" s="19">
+        <v>40</v>
+      </c>
+      <c r="M173" s="19">
+        <v>40</v>
+      </c>
       <c r="N173" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O173" s="21"/>
-      <c r="P173" s="21"/>
-      <c r="Q173" s="21"/>
+        <v>120</v>
+      </c>
+      <c r="O173" s="21">
+        <v>40</v>
+      </c>
+      <c r="P173" s="21">
+        <v>40</v>
+      </c>
+      <c r="Q173" s="21">
+        <v>40</v>
+      </c>
       <c r="R173" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S173" s="19">
         <v>120</v>
       </c>
       <c r="T173" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U173" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V173" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W173" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="X173" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y173" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z173" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA173" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB173" s="9">
         <v>39.270000000000003</v>
@@ -23856,14 +25000,14 @@
       </c>
       <c r="AE173" s="10">
         <f t="shared" si="91"/>
-        <v>8716.7999999999993</v>
+        <v>15012.3</v>
       </c>
       <c r="AF173" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG173" s="11">
         <f t="shared" si="86"/>
-        <v>566.59199999999998</v>
+        <v>975.79949999999997</v>
       </c>
       <c r="AH173" s="80">
         <f t="shared" si="92"/>
@@ -23871,78 +25015,110 @@
       </c>
       <c r="AI173" s="10">
         <f t="shared" si="93"/>
-        <v>8150.2079999999996</v>
+        <v>14036.5005</v>
       </c>
       <c r="AJ173" s="5">
         <v>0.18</v>
       </c>
       <c r="AK173" s="12">
         <f t="shared" si="94"/>
-        <v>1467.0374399999998</v>
+        <v>2526.5700899999997</v>
       </c>
       <c r="AL173" s="10">
         <f t="shared" si="95"/>
-        <v>9617.2454399999988</v>
+        <v>16563.070589999999</v>
       </c>
       <c r="AP173" s="13"/>
     </row>
     <row r="174" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A174" s="18"/>
-      <c r="C174" s="19"/>
-      <c r="E174" s="6"/>
-      <c r="F174" s="20"/>
-      <c r="G174" s="20"/>
-      <c r="H174" s="20"/>
-      <c r="I174" s="6"/>
+      <c r="A174" s="18">
+        <v>46190</v>
+      </c>
+      <c r="B174" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C174" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D174" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E174" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F174" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="G174" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="H174" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="I174" s="6" t="s">
+        <v>312</v>
+      </c>
       <c r="J174" s="70"/>
-      <c r="K174" s="21"/>
-      <c r="L174" s="21"/>
-      <c r="M174" s="21"/>
+      <c r="K174" s="21">
+        <v>40</v>
+      </c>
+      <c r="L174" s="21">
+        <v>40</v>
+      </c>
+      <c r="M174" s="21">
+        <v>40</v>
+      </c>
       <c r="N174" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O174" s="19"/>
-      <c r="P174" s="19"/>
-      <c r="Q174" s="19"/>
+        <v>120</v>
+      </c>
+      <c r="O174" s="19">
+        <v>40</v>
+      </c>
+      <c r="P174" s="19">
+        <v>40</v>
+      </c>
+      <c r="Q174" s="19">
+        <v>40</v>
+      </c>
       <c r="R174" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S174" s="19">
         <v>40</v>
       </c>
       <c r="T174" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U174" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V174" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W174" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="X174" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y174" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z174" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA174" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB174" s="9">
         <v>39.270000000000003</v>
@@ -23955,14 +25131,14 @@
       </c>
       <c r="AE174" s="10">
         <f t="shared" si="91"/>
-        <v>2905.6</v>
+        <v>9201.1</v>
       </c>
       <c r="AF174" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG174" s="11">
         <f t="shared" si="86"/>
-        <v>188.864</v>
+        <v>598.07150000000001</v>
       </c>
       <c r="AH174" s="80">
         <f t="shared" si="92"/>
@@ -23970,78 +25146,110 @@
       </c>
       <c r="AI174" s="10">
         <f t="shared" si="93"/>
-        <v>2716.7359999999999</v>
+        <v>8603.0285000000003</v>
       </c>
       <c r="AJ174" s="5">
         <v>0.18</v>
       </c>
       <c r="AK174" s="12">
         <f t="shared" si="94"/>
-        <v>489.01247999999998</v>
+        <v>1548.54513</v>
       </c>
       <c r="AL174" s="10">
         <f t="shared" si="95"/>
-        <v>3205.7484799999997</v>
+        <v>10151.573630000001</v>
       </c>
       <c r="AP174" s="13"/>
     </row>
     <row r="175" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A175" s="18"/>
-      <c r="C175" s="19"/>
-      <c r="E175" s="6"/>
-      <c r="F175" s="20"/>
-      <c r="G175" s="20"/>
-      <c r="H175" s="20"/>
-      <c r="I175" s="6"/>
+      <c r="A175" s="18">
+        <v>46190</v>
+      </c>
+      <c r="B175" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C175" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D175" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E175" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F175" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="G175" s="20" t="s">
+        <v>301</v>
+      </c>
+      <c r="H175" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="I175" s="6" t="s">
+        <v>313</v>
+      </c>
       <c r="J175" s="70"/>
-      <c r="K175" s="21"/>
-      <c r="L175" s="21"/>
-      <c r="M175" s="21"/>
+      <c r="K175" s="21">
+        <v>40</v>
+      </c>
+      <c r="L175" s="21">
+        <v>40</v>
+      </c>
+      <c r="M175" s="21">
+        <v>40</v>
+      </c>
       <c r="N175" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O175" s="19"/>
-      <c r="P175" s="19"/>
-      <c r="Q175" s="19"/>
+        <v>120</v>
+      </c>
+      <c r="O175" s="19">
+        <v>40</v>
+      </c>
+      <c r="P175" s="19">
+        <v>40</v>
+      </c>
+      <c r="Q175" s="19">
+        <v>40</v>
+      </c>
       <c r="R175" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S175" s="19">
         <v>60</v>
       </c>
       <c r="T175" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U175" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V175" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W175" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="X175" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y175" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z175" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA175" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB175" s="9">
         <v>39.270000000000003</v>
@@ -24054,14 +25262,14 @@
       </c>
       <c r="AE175" s="10">
         <f t="shared" si="91"/>
-        <v>4358.3999999999996</v>
+        <v>10653.9</v>
       </c>
       <c r="AF175" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG175" s="11">
         <f t="shared" si="86"/>
-        <v>283.29599999999999</v>
+        <v>692.50350000000003</v>
       </c>
       <c r="AH175" s="80">
         <f t="shared" si="92"/>
@@ -24069,78 +25277,110 @@
       </c>
       <c r="AI175" s="10">
         <f t="shared" si="93"/>
-        <v>4075.1039999999998</v>
+        <v>9961.3964999999989</v>
       </c>
       <c r="AJ175" s="5">
         <v>0.18</v>
       </c>
       <c r="AK175" s="12">
         <f t="shared" si="94"/>
-        <v>733.51871999999992</v>
+        <v>1793.0513699999997</v>
       </c>
       <c r="AL175" s="10">
         <f t="shared" si="95"/>
-        <v>4808.6227199999994</v>
+        <v>11754.447869999998</v>
       </c>
       <c r="AP175" s="13"/>
     </row>
     <row r="176" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A176" s="18"/>
-      <c r="C176" s="19"/>
-      <c r="E176" s="6"/>
-      <c r="F176" s="20"/>
-      <c r="G176" s="20"/>
-      <c r="H176" s="20"/>
-      <c r="I176" s="6"/>
+      <c r="A176" s="18">
+        <v>46190</v>
+      </c>
+      <c r="B176" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C176" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D176" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E176" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F176" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="G176" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="H176" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="I176" s="6" t="s">
+        <v>314</v>
+      </c>
       <c r="J176" s="70"/>
-      <c r="K176" s="21"/>
-      <c r="L176" s="21"/>
-      <c r="M176" s="21"/>
+      <c r="K176" s="21">
+        <v>80</v>
+      </c>
+      <c r="L176" s="21">
+        <v>80</v>
+      </c>
+      <c r="M176" s="21">
+        <v>80</v>
+      </c>
       <c r="N176" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O176" s="19"/>
-      <c r="P176" s="19"/>
-      <c r="Q176" s="19"/>
+        <v>240</v>
+      </c>
+      <c r="O176" s="19">
+        <v>80</v>
+      </c>
+      <c r="P176" s="19">
+        <v>80</v>
+      </c>
+      <c r="Q176" s="19">
+        <v>80</v>
+      </c>
       <c r="R176" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="S176" s="19">
         <v>80</v>
       </c>
       <c r="T176" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U176" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V176" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W176" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X176" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y176" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z176" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA176" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB176" s="9">
         <v>39.270000000000003</v>
@@ -24153,14 +25393,14 @@
       </c>
       <c r="AE176" s="10">
         <f t="shared" si="91"/>
-        <v>5811.2</v>
+        <v>18402.2</v>
       </c>
       <c r="AF176" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG176" s="11">
         <f t="shared" si="86"/>
-        <v>377.72800000000001</v>
+        <v>1196.143</v>
       </c>
       <c r="AH176" s="80">
         <f t="shared" si="92"/>
@@ -24168,78 +25408,110 @@
       </c>
       <c r="AI176" s="10">
         <f t="shared" si="93"/>
-        <v>5433.4719999999998</v>
+        <v>17206.057000000001</v>
       </c>
       <c r="AJ176" s="5">
         <v>0.18</v>
       </c>
       <c r="AK176" s="12">
         <f t="shared" si="94"/>
-        <v>978.02495999999996</v>
+        <v>3097.0902599999999</v>
       </c>
       <c r="AL176" s="10">
         <f t="shared" si="95"/>
-        <v>6411.4969599999995</v>
+        <v>20303.147260000002</v>
       </c>
       <c r="AP176" s="13"/>
     </row>
     <row r="177" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A177" s="18"/>
-      <c r="C177" s="19"/>
-      <c r="E177" s="6"/>
-      <c r="F177" s="20"/>
-      <c r="G177" s="20"/>
-      <c r="H177" s="20"/>
-      <c r="I177" s="6"/>
+      <c r="A177" s="18">
+        <v>46190</v>
+      </c>
+      <c r="B177" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C177" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D177" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E177" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F177" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="G177" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="H177" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="I177" s="6" t="s">
+        <v>315</v>
+      </c>
       <c r="J177" s="70"/>
-      <c r="K177" s="21"/>
-      <c r="L177" s="21"/>
-      <c r="M177" s="21"/>
+      <c r="K177" s="21">
+        <v>40</v>
+      </c>
+      <c r="L177" s="21">
+        <v>40</v>
+      </c>
+      <c r="M177" s="21">
+        <v>40</v>
+      </c>
       <c r="N177" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O177" s="19"/>
-      <c r="P177" s="19"/>
-      <c r="Q177" s="19"/>
+        <v>120</v>
+      </c>
+      <c r="O177" s="19">
+        <v>40</v>
+      </c>
+      <c r="P177" s="19">
+        <v>40</v>
+      </c>
+      <c r="Q177" s="19">
+        <v>40</v>
+      </c>
       <c r="R177" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S177" s="19">
         <v>40</v>
       </c>
       <c r="T177" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U177" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V177" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W177" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="X177" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y177" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z177" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA177" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB177" s="9">
         <v>39.270000000000003</v>
@@ -24252,14 +25524,14 @@
       </c>
       <c r="AE177" s="10">
         <f t="shared" si="91"/>
-        <v>2905.6</v>
+        <v>9201.1</v>
       </c>
       <c r="AF177" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG177" s="11">
         <f t="shared" si="86"/>
-        <v>188.864</v>
+        <v>598.07150000000001</v>
       </c>
       <c r="AH177" s="80">
         <f t="shared" si="92"/>
@@ -24267,78 +25539,110 @@
       </c>
       <c r="AI177" s="10">
         <f t="shared" si="93"/>
-        <v>2716.7359999999999</v>
+        <v>8603.0285000000003</v>
       </c>
       <c r="AJ177" s="5">
         <v>0.18</v>
       </c>
       <c r="AK177" s="12">
         <f t="shared" si="94"/>
-        <v>489.01247999999998</v>
+        <v>1548.54513</v>
       </c>
       <c r="AL177" s="10">
         <f t="shared" si="95"/>
-        <v>3205.7484799999997</v>
+        <v>10151.573630000001</v>
       </c>
       <c r="AP177" s="13"/>
     </row>
     <row r="178" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A178" s="18"/>
-      <c r="C178" s="19"/>
-      <c r="E178" s="6"/>
-      <c r="F178" s="20"/>
-      <c r="G178" s="20"/>
-      <c r="H178" s="20"/>
-      <c r="I178" s="6"/>
+      <c r="A178" s="18">
+        <v>46190</v>
+      </c>
+      <c r="B178" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C178" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D178" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E178" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F178" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="G178" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="H178" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="I178" s="6" t="s">
+        <v>316</v>
+      </c>
       <c r="J178" s="70"/>
-      <c r="K178" s="19"/>
-      <c r="L178" s="19"/>
-      <c r="M178" s="19"/>
+      <c r="K178" s="19">
+        <v>80</v>
+      </c>
+      <c r="L178" s="19">
+        <v>80</v>
+      </c>
+      <c r="M178" s="19">
+        <v>80</v>
+      </c>
       <c r="N178" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O178" s="21"/>
-      <c r="P178" s="21"/>
-      <c r="Q178" s="21"/>
+        <v>240</v>
+      </c>
+      <c r="O178" s="21">
+        <v>80</v>
+      </c>
+      <c r="P178" s="21">
+        <v>80</v>
+      </c>
+      <c r="Q178" s="21">
+        <v>80</v>
+      </c>
       <c r="R178" s="9">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="S178" s="19">
         <v>40</v>
       </c>
       <c r="T178" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U178" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V178" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W178" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X178" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y178" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z178" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA178" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB178" s="9">
         <v>39.270000000000003</v>
@@ -24351,14 +25655,14 @@
       </c>
       <c r="AE178" s="10">
         <f t="shared" si="91"/>
-        <v>2905.6</v>
+        <v>15496.6</v>
       </c>
       <c r="AF178" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG178" s="11">
         <f t="shared" si="86"/>
-        <v>188.864</v>
+        <v>1007.2790000000001</v>
       </c>
       <c r="AH178" s="80">
         <f t="shared" si="92"/>
@@ -24366,78 +25670,110 @@
       </c>
       <c r="AI178" s="10">
         <f t="shared" si="93"/>
-        <v>2716.7359999999999</v>
+        <v>14489.321</v>
       </c>
       <c r="AJ178" s="5">
         <v>0.18</v>
       </c>
       <c r="AK178" s="12">
         <f t="shared" si="94"/>
-        <v>489.01247999999998</v>
+        <v>2608.0777800000001</v>
       </c>
       <c r="AL178" s="10">
         <f t="shared" si="95"/>
-        <v>3205.7484799999997</v>
+        <v>17097.39878</v>
       </c>
       <c r="AP178" s="13"/>
     </row>
     <row r="179" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A179" s="18"/>
-      <c r="C179" s="19"/>
-      <c r="E179" s="6"/>
-      <c r="F179" s="20"/>
-      <c r="G179" s="20"/>
-      <c r="H179" s="20"/>
-      <c r="I179" s="6"/>
+      <c r="A179" s="18">
+        <v>46190</v>
+      </c>
+      <c r="B179" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C179" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D179" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E179" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F179" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="G179" s="20" t="s">
+        <v>305</v>
+      </c>
+      <c r="H179" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="I179" s="6" t="s">
+        <v>317</v>
+      </c>
       <c r="J179" s="70"/>
-      <c r="K179" s="19"/>
-      <c r="L179" s="19"/>
-      <c r="M179" s="19"/>
+      <c r="K179" s="19">
+        <v>80</v>
+      </c>
+      <c r="L179" s="19">
+        <v>80</v>
+      </c>
+      <c r="M179" s="19">
+        <v>80</v>
+      </c>
       <c r="N179" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O179" s="19"/>
-      <c r="P179" s="19"/>
-      <c r="Q179" s="19"/>
+        <v>240</v>
+      </c>
+      <c r="O179" s="19">
+        <v>80</v>
+      </c>
+      <c r="P179" s="19">
+        <v>80</v>
+      </c>
+      <c r="Q179" s="19">
+        <v>80</v>
+      </c>
       <c r="R179" s="9">
         <f t="shared" ref="R179:R220" si="96">SUM(O179:Q179)</f>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="S179" s="19">
         <v>480</v>
       </c>
       <c r="T179" s="19">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U179" s="19">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V179" s="19">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W179" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X179" s="19">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y179" s="19">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z179" s="19">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA179" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB179" s="9">
         <v>39.270000000000003</v>
@@ -24450,14 +25786,14 @@
       </c>
       <c r="AE179" s="10">
         <f t="shared" si="91"/>
-        <v>34867.199999999997</v>
+        <v>47458.2</v>
       </c>
       <c r="AF179" s="22">
         <v>0.1</v>
       </c>
       <c r="AG179" s="11">
         <f t="shared" si="86"/>
-        <v>3486.72</v>
+        <v>4745.82</v>
       </c>
       <c r="AH179" s="80">
         <f t="shared" si="92"/>
@@ -24465,78 +25801,110 @@
       </c>
       <c r="AI179" s="10">
         <f t="shared" si="93"/>
-        <v>31380.479999999996</v>
+        <v>42712.38</v>
       </c>
       <c r="AJ179" s="5">
         <v>0.18</v>
       </c>
       <c r="AK179" s="12">
         <f t="shared" si="94"/>
-        <v>5648.4863999999989</v>
+        <v>7688.2283999999991</v>
       </c>
       <c r="AL179" s="10">
         <f t="shared" si="95"/>
-        <v>37028.966399999998</v>
+        <v>50400.608399999997</v>
       </c>
       <c r="AP179" s="13"/>
     </row>
     <row r="180" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A180" s="18"/>
-      <c r="C180" s="19"/>
-      <c r="E180" s="6"/>
-      <c r="F180" s="20"/>
-      <c r="G180" s="20"/>
-      <c r="H180" s="20"/>
-      <c r="I180" s="6"/>
+      <c r="A180" s="18">
+        <v>46190</v>
+      </c>
+      <c r="B180" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C180" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D180" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E180" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F180" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="G180" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="H180" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="I180" s="6" t="s">
+        <v>318</v>
+      </c>
       <c r="J180" s="70"/>
-      <c r="K180" s="21"/>
-      <c r="L180" s="21"/>
-      <c r="M180" s="21"/>
+      <c r="K180" s="21">
+        <v>40</v>
+      </c>
+      <c r="L180" s="21">
+        <v>40</v>
+      </c>
+      <c r="M180" s="21">
+        <v>40</v>
+      </c>
       <c r="N180" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O180" s="19"/>
-      <c r="P180" s="19"/>
-      <c r="Q180" s="19"/>
+        <v>120</v>
+      </c>
+      <c r="O180" s="19">
+        <v>40</v>
+      </c>
+      <c r="P180" s="19">
+        <v>40</v>
+      </c>
+      <c r="Q180" s="19">
+        <v>40</v>
+      </c>
       <c r="R180" s="9">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S180" s="19">
         <v>120</v>
       </c>
       <c r="T180" s="19">
         <f t="shared" ref="T180:T221" si="97">K180/10</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U180" s="19">
         <f t="shared" ref="U180:U221" si="98">L180/10</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V180" s="19">
         <f t="shared" ref="V180:V221" si="99">M180/10</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W180" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="X180" s="19">
         <f t="shared" ref="X180:X221" si="100">O180/10</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y180" s="19">
         <f t="shared" ref="Y180:Y221" si="101">P180/10</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z180" s="19">
         <f t="shared" ref="Z180:Z221" si="102">Q180/10</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA180" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB180" s="9">
         <v>39.270000000000003</v>
@@ -24549,14 +25917,14 @@
       </c>
       <c r="AE180" s="10">
         <f t="shared" si="91"/>
-        <v>8716.7999999999993</v>
+        <v>15012.3</v>
       </c>
       <c r="AF180" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG180" s="11">
         <f t="shared" ref="AG180:AG221" si="103">AE180*AF180</f>
-        <v>566.59199999999998</v>
+        <v>975.79949999999997</v>
       </c>
       <c r="AH180" s="80">
         <f t="shared" si="92"/>
@@ -24564,78 +25932,110 @@
       </c>
       <c r="AI180" s="10">
         <f t="shared" si="93"/>
-        <v>8150.2079999999996</v>
+        <v>14036.5005</v>
       </c>
       <c r="AJ180" s="5">
         <v>0.18</v>
       </c>
       <c r="AK180" s="12">
         <f t="shared" si="94"/>
-        <v>1467.0374399999998</v>
+        <v>2526.5700899999997</v>
       </c>
       <c r="AL180" s="10">
         <f t="shared" si="95"/>
-        <v>9617.2454399999988</v>
+        <v>16563.070589999999</v>
       </c>
       <c r="AP180" s="13"/>
     </row>
     <row r="181" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A181" s="18"/>
-      <c r="C181" s="19"/>
-      <c r="E181" s="6"/>
-      <c r="F181" s="20"/>
-      <c r="G181" s="20"/>
-      <c r="H181" s="20"/>
-      <c r="I181" s="6"/>
+      <c r="A181" s="18">
+        <v>46190</v>
+      </c>
+      <c r="B181" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C181" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D181" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E181" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F181" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="G181" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="H181" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="I181" s="6" t="s">
+        <v>319</v>
+      </c>
       <c r="J181" s="70"/>
-      <c r="K181" s="21"/>
-      <c r="L181" s="21"/>
-      <c r="M181" s="21"/>
+      <c r="K181" s="21">
+        <v>40</v>
+      </c>
+      <c r="L181" s="21">
+        <v>40</v>
+      </c>
+      <c r="M181" s="21">
+        <v>40</v>
+      </c>
       <c r="N181" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O181" s="19"/>
-      <c r="P181" s="21"/>
-      <c r="Q181" s="19"/>
+        <v>120</v>
+      </c>
+      <c r="O181" s="19">
+        <v>40</v>
+      </c>
+      <c r="P181" s="21">
+        <v>40</v>
+      </c>
+      <c r="Q181" s="19">
+        <v>40</v>
+      </c>
       <c r="R181" s="9">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S181" s="19">
         <v>20</v>
       </c>
       <c r="T181" s="19">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U181" s="19">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V181" s="19">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W181" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="X181" s="19">
         <f t="shared" si="100"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y181" s="19">
         <f t="shared" si="101"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z181" s="19">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA181" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB181" s="9">
         <v>39.270000000000003</v>
@@ -24648,14 +26048,14 @@
       </c>
       <c r="AE181" s="10">
         <f t="shared" si="91"/>
-        <v>1452.8</v>
+        <v>7748.3</v>
       </c>
       <c r="AF181" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG181" s="11">
         <f t="shared" si="103"/>
-        <v>94.432000000000002</v>
+        <v>503.63950000000006</v>
       </c>
       <c r="AH181" s="80">
         <f t="shared" si="92"/>
@@ -24663,78 +26063,110 @@
       </c>
       <c r="AI181" s="10">
         <f t="shared" si="93"/>
-        <v>1358.3679999999999</v>
+        <v>7244.6605</v>
       </c>
       <c r="AJ181" s="5">
         <v>0.18</v>
       </c>
       <c r="AK181" s="12">
         <f t="shared" si="94"/>
-        <v>244.50623999999999</v>
+        <v>1304.03889</v>
       </c>
       <c r="AL181" s="10">
         <f t="shared" si="95"/>
-        <v>1602.8742399999999</v>
+        <v>8548.6993899999998</v>
       </c>
       <c r="AP181" s="13"/>
     </row>
     <row r="182" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A182" s="18"/>
-      <c r="C182" s="19"/>
-      <c r="E182" s="6"/>
-      <c r="F182" s="20"/>
-      <c r="G182" s="20"/>
-      <c r="H182" s="20"/>
-      <c r="I182" s="6"/>
+      <c r="A182" s="18">
+        <v>46190</v>
+      </c>
+      <c r="B182" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C182" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D182" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E182" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F182" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="G182" s="20" t="s">
+        <v>308</v>
+      </c>
+      <c r="H182" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="I182" s="6" t="s">
+        <v>320</v>
+      </c>
       <c r="J182" s="70"/>
-      <c r="K182" s="21"/>
-      <c r="L182" s="21"/>
-      <c r="M182" s="21"/>
+      <c r="K182" s="21">
+        <v>40</v>
+      </c>
+      <c r="L182" s="21">
+        <v>40</v>
+      </c>
+      <c r="M182" s="21">
+        <v>40</v>
+      </c>
       <c r="N182" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O182" s="19"/>
-      <c r="P182" s="19"/>
-      <c r="Q182" s="19"/>
+        <v>120</v>
+      </c>
+      <c r="O182" s="19">
+        <v>40</v>
+      </c>
+      <c r="P182" s="19">
+        <v>40</v>
+      </c>
+      <c r="Q182" s="19">
+        <v>40</v>
+      </c>
       <c r="R182" s="9">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S182" s="19">
         <v>60</v>
       </c>
       <c r="T182" s="19">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U182" s="19">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V182" s="19">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W182" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="X182" s="19">
         <f t="shared" si="100"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y182" s="19">
         <f t="shared" si="101"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z182" s="19">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA182" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB182" s="9">
         <v>39.270000000000003</v>
@@ -24747,14 +26179,14 @@
       </c>
       <c r="AE182" s="10">
         <f t="shared" si="91"/>
-        <v>4358.3999999999996</v>
+        <v>10653.9</v>
       </c>
       <c r="AF182" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG182" s="11">
         <f t="shared" si="103"/>
-        <v>283.29599999999999</v>
+        <v>692.50350000000003</v>
       </c>
       <c r="AH182" s="80">
         <f t="shared" si="92"/>
@@ -24762,78 +26194,110 @@
       </c>
       <c r="AI182" s="10">
         <f t="shared" si="93"/>
-        <v>4075.1039999999998</v>
+        <v>9961.3964999999989</v>
       </c>
       <c r="AJ182" s="5">
         <v>0.18</v>
       </c>
       <c r="AK182" s="12">
         <f t="shared" si="94"/>
-        <v>733.51871999999992</v>
+        <v>1793.0513699999997</v>
       </c>
       <c r="AL182" s="10">
         <f t="shared" si="95"/>
-        <v>4808.6227199999994</v>
+        <v>11754.447869999998</v>
       </c>
       <c r="AP182" s="13"/>
     </row>
     <row r="183" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A183" s="18"/>
-      <c r="C183" s="19"/>
-      <c r="E183" s="6"/>
-      <c r="F183" s="20"/>
-      <c r="G183" s="20"/>
-      <c r="H183" s="20"/>
-      <c r="I183" s="6"/>
+      <c r="A183" s="18">
+        <v>46190</v>
+      </c>
+      <c r="B183" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C183" s="82">
+        <v>1129.1428571428601</v>
+      </c>
+      <c r="D183" s="82">
+        <v>43440.392857143299</v>
+      </c>
+      <c r="E183" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F183" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="G183" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="H183" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="I183" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="J183" s="70"/>
-      <c r="K183" s="21"/>
-      <c r="L183" s="21"/>
-      <c r="M183" s="21"/>
+      <c r="K183" s="21">
+        <v>80</v>
+      </c>
+      <c r="L183" s="21">
+        <v>80</v>
+      </c>
+      <c r="M183" s="21">
+        <v>80</v>
+      </c>
       <c r="N183" s="9">
         <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-      <c r="O183" s="19"/>
-      <c r="P183" s="19"/>
-      <c r="Q183" s="19"/>
+        <v>240</v>
+      </c>
+      <c r="O183" s="19">
+        <v>80</v>
+      </c>
+      <c r="P183" s="19">
+        <v>80</v>
+      </c>
+      <c r="Q183" s="19">
+        <v>80</v>
+      </c>
       <c r="R183" s="9">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="S183" s="19">
         <v>40</v>
       </c>
       <c r="T183" s="19">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U183" s="19">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V183" s="19">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W183" s="9">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X183" s="19">
         <f t="shared" si="100"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y183" s="19">
         <f t="shared" si="101"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z183" s="19">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA183" s="9">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB183" s="9">
         <v>39.270000000000003</v>
@@ -24846,14 +26310,14 @@
       </c>
       <c r="AE183" s="10">
         <f t="shared" si="91"/>
-        <v>2905.6</v>
+        <v>15496.6</v>
       </c>
       <c r="AF183" s="22">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG183" s="11">
         <f t="shared" si="103"/>
-        <v>188.864</v>
+        <v>1007.2790000000001</v>
       </c>
       <c r="AH183" s="80">
         <f t="shared" si="92"/>
@@ -24861,18 +26325,18 @@
       </c>
       <c r="AI183" s="10">
         <f t="shared" si="93"/>
-        <v>2716.7359999999999</v>
+        <v>14489.321</v>
       </c>
       <c r="AJ183" s="5">
         <v>0.18</v>
       </c>
       <c r="AK183" s="12">
         <f t="shared" si="94"/>
-        <v>489.01247999999998</v>
+        <v>2608.0777800000001</v>
       </c>
       <c r="AL183" s="10">
         <f t="shared" si="95"/>
-        <v>3205.7484799999997</v>
+        <v>17097.39878</v>
       </c>
       <c r="AP183" s="13"/>
     </row>
@@ -49735,39 +51199,39 @@
       <c r="I435" s="6"/>
       <c r="J435" s="6">
         <f t="shared" ref="J435:AA435" si="176">SUM(J3:J434)</f>
-        <v>4643</v>
+        <v>5069</v>
       </c>
       <c r="K435" s="6">
         <f t="shared" si="176"/>
-        <v>10735</v>
+        <v>12077</v>
       </c>
       <c r="L435" s="6">
         <f t="shared" si="176"/>
-        <v>8997</v>
+        <v>10335</v>
       </c>
       <c r="M435" s="6">
         <f t="shared" si="176"/>
-        <v>11844</v>
+        <v>13225</v>
       </c>
       <c r="N435" s="6">
         <f t="shared" si="176"/>
-        <v>31576</v>
+        <v>35637</v>
       </c>
       <c r="O435" s="6">
         <f t="shared" si="176"/>
-        <v>14267</v>
+        <v>15715</v>
       </c>
       <c r="P435" s="6">
         <f t="shared" si="176"/>
-        <v>12452</v>
+        <v>13795</v>
       </c>
       <c r="Q435" s="6">
         <f t="shared" si="176"/>
-        <v>19894</v>
+        <v>21616</v>
       </c>
       <c r="R435" s="6">
         <f t="shared" si="176"/>
-        <v>46613</v>
+        <v>51126</v>
       </c>
       <c r="S435" s="6">
         <f t="shared" si="176"/>
@@ -49775,63 +51239,63 @@
       </c>
       <c r="T435" s="6">
         <f t="shared" si="176"/>
-        <v>1073.1000000000004</v>
+        <v>1207.3000000000002</v>
       </c>
       <c r="U435" s="6">
         <f t="shared" si="176"/>
-        <v>899.40000000000043</v>
+        <v>1033.2000000000005</v>
       </c>
       <c r="V435" s="6">
         <f t="shared" si="176"/>
-        <v>1184.25</v>
+        <v>1322.3500000000004</v>
       </c>
       <c r="W435" s="6">
         <f t="shared" si="176"/>
-        <v>3156.7499999999991</v>
+        <v>3562.849999999999</v>
       </c>
       <c r="X435" s="6">
         <f t="shared" si="176"/>
-        <v>1426.6999999999998</v>
+        <v>1571.4999999999998</v>
       </c>
       <c r="Y435" s="6">
         <f t="shared" si="176"/>
-        <v>1245.2000000000003</v>
+        <v>1379.5000000000002</v>
       </c>
       <c r="Z435" s="6">
         <f t="shared" si="176"/>
-        <v>1989.4</v>
+        <v>2161.6</v>
       </c>
       <c r="AA435" s="6">
         <f t="shared" si="176"/>
-        <v>4661.2999999999993</v>
+        <v>5112.5999999999995</v>
       </c>
       <c r="AB435" s="6"/>
       <c r="AC435" s="6"/>
       <c r="AD435" s="6"/>
       <c r="AE435" s="6">
         <f>SUM(AE3:AE434)</f>
-        <v>4754510.8300000029</v>
+        <v>4984290.0624999981</v>
       </c>
       <c r="AF435" s="8"/>
       <c r="AG435" s="6">
         <f>SUM(AG3:AG434)</f>
-        <v>387820.45836729929</v>
+        <v>403729.63229229901</v>
       </c>
       <c r="AH435" s="6">
         <f>SUM(AH3:AH434)</f>
-        <v>6381.5713499999993</v>
+        <v>6967.0870499999983</v>
       </c>
       <c r="AI435" s="6">
         <f>SUM(AI3:AI434)</f>
-        <v>4366621.6491327025</v>
+        <v>4580491.7077076975</v>
       </c>
       <c r="AK435" s="6">
         <f>SUM(AK3:AK434)</f>
-        <v>785991.89684388658</v>
+        <v>824488.50738738722</v>
       </c>
       <c r="AL435" s="6">
         <f>SUM(AL3:AL434)</f>
-        <v>5152613.5459765792</v>
+        <v>5404980.2150950748</v>
       </c>
       <c r="AP435" s="13"/>
     </row>
@@ -49908,39 +51372,39 @@
       </c>
       <c r="J439" s="77">
         <f t="shared" ref="J439:AF439" si="177">+J435/40</f>
-        <v>116.075</v>
+        <v>126.72499999999999</v>
       </c>
       <c r="K439" s="78">
         <f t="shared" si="177"/>
-        <v>268.375</v>
+        <v>301.92500000000001</v>
       </c>
       <c r="L439" s="78">
         <f t="shared" si="177"/>
-        <v>224.92500000000001</v>
+        <v>258.375</v>
       </c>
       <c r="M439" s="78">
         <f t="shared" si="177"/>
-        <v>296.10000000000002</v>
+        <v>330.625</v>
       </c>
       <c r="N439" s="77">
         <f t="shared" si="177"/>
-        <v>789.4</v>
+        <v>890.92499999999995</v>
       </c>
       <c r="O439" s="78">
         <f t="shared" si="177"/>
-        <v>356.67500000000001</v>
+        <v>392.875</v>
       </c>
       <c r="P439" s="78">
         <f t="shared" si="177"/>
-        <v>311.3</v>
+        <v>344.875</v>
       </c>
       <c r="Q439" s="78">
         <f t="shared" si="177"/>
-        <v>497.35</v>
+        <v>540.4</v>
       </c>
       <c r="R439" s="77">
         <f t="shared" si="177"/>
-        <v>1165.325</v>
+        <v>1278.1500000000001</v>
       </c>
       <c r="S439" s="16">
         <f t="shared" si="177"/>
@@ -49948,35 +51412,35 @@
       </c>
       <c r="T439" s="16">
         <f t="shared" si="177"/>
-        <v>26.827500000000008</v>
+        <v>30.182500000000005</v>
       </c>
       <c r="U439" s="16">
         <f t="shared" si="177"/>
-        <v>22.48500000000001</v>
+        <v>25.830000000000013</v>
       </c>
       <c r="V439" s="16">
         <f t="shared" si="177"/>
-        <v>29.606249999999999</v>
+        <v>33.058750000000011</v>
       </c>
       <c r="W439" s="16">
         <f t="shared" si="177"/>
-        <v>78.918749999999974</v>
+        <v>89.071249999999978</v>
       </c>
       <c r="X439" s="16">
         <f t="shared" si="177"/>
-        <v>35.667499999999997</v>
+        <v>39.287499999999994</v>
       </c>
       <c r="Y439" s="16">
         <f t="shared" si="177"/>
-        <v>31.130000000000006</v>
+        <v>34.487500000000004</v>
       </c>
       <c r="Z439" s="16">
         <f t="shared" si="177"/>
-        <v>49.734999999999999</v>
+        <v>54.04</v>
       </c>
       <c r="AA439" s="16">
         <f t="shared" si="177"/>
-        <v>116.53249999999998</v>
+        <v>127.81499999999998</v>
       </c>
       <c r="AB439" s="16"/>
       <c r="AC439">
@@ -49989,7 +51453,7 @@
       </c>
       <c r="AE439">
         <f t="shared" si="177"/>
-        <v>118862.77075000007</v>
+        <v>124607.25156249995</v>
       </c>
       <c r="AF439">
         <f t="shared" si="177"/>
@@ -50017,13 +51481,14 @@
     <filterColumn colId="25" showButton="0"/>
   </autoFilter>
   <mergeCells count="27">
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AN1:AN2"/>
     <mergeCell ref="AG1:AG2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
@@ -50036,14 +51501,13 @@
     <mergeCell ref="AE1:AE2"/>
     <mergeCell ref="AF1:AF2"/>
     <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -50114,11 +51578,11 @@
       <c r="F7" s="29"/>
       <c r="G7" s="30">
         <f>('STT Report'!O435+'STT Report'!X435)/40</f>
-        <v>392.34250000000003</v>
+        <v>432.16250000000002</v>
       </c>
       <c r="H7" s="31">
         <f>E7+F7-G7</f>
-        <v>290.8775</v>
+        <v>251.0575</v>
       </c>
     </row>
     <row r="8" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -50133,11 +51597,11 @@
       </c>
       <c r="G8" s="30">
         <f>('STT Report'!P435+'STT Report'!Y435)/40</f>
-        <v>342.43</v>
+        <v>379.36250000000001</v>
       </c>
       <c r="H8" s="31">
         <f>E8+F8-G8</f>
-        <v>-8.7700000000000387</v>
+        <v>-45.702500000000043</v>
       </c>
     </row>
     <row r="9" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -50150,11 +51614,11 @@
       <c r="F9" s="32"/>
       <c r="G9" s="30">
         <f>('STT Report'!Q435+'STT Report'!Z435)/40</f>
-        <v>547.08500000000004</v>
+        <v>594.43999999999994</v>
       </c>
       <c r="H9" s="31">
         <f>E9+F9-G9</f>
-        <v>-212.22500000000002</v>
+        <v>-259.57999999999993</v>
       </c>
     </row>
     <row r="10" spans="4:8" x14ac:dyDescent="0.35">
@@ -50171,11 +51635,11 @@
       </c>
       <c r="G10" s="36">
         <f>SUM(G7:G9)</f>
-        <v>1281.8575000000001</v>
+        <v>1405.9650000000001</v>
       </c>
       <c r="H10" s="37">
         <f>SUM(H7:H9)</f>
-        <v>69.882499999999936</v>
+        <v>-54.224999999999966</v>
       </c>
     </row>
     <row r="11" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -50188,11 +51652,11 @@
       </c>
       <c r="G11" s="73">
         <f>'STT Report'!J435/40</f>
-        <v>116.075</v>
+        <v>126.72499999999999</v>
       </c>
       <c r="H11" s="31">
         <f t="shared" ref="H11:H13" si="0">(E11+F11)-G11</f>
-        <v>383.92500000000001</v>
+        <v>373.27499999999998</v>
       </c>
     </row>
     <row r="12" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -50226,11 +51690,11 @@
       </c>
       <c r="G14" s="34">
         <f>SUM(G11:G13)</f>
-        <v>116.075</v>
+        <v>126.72499999999999</v>
       </c>
       <c r="H14" s="37">
         <f>SUM(H11:H13)</f>
-        <v>383.92500000000001</v>
+        <v>373.27499999999998</v>
       </c>
     </row>
     <row r="15" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -50243,11 +51707,11 @@
       <c r="F15" s="29"/>
       <c r="G15" s="30">
         <f>('STT Report'!K435+'STT Report'!T435)/40</f>
-        <v>295.20249999999999</v>
+        <v>332.10749999999996</v>
       </c>
       <c r="H15" s="31">
         <f>E15+F15-G15</f>
-        <v>-67.082499999999982</v>
+        <v>-103.98749999999995</v>
       </c>
     </row>
     <row r="16" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -50260,11 +51724,11 @@
       <c r="F16" s="32"/>
       <c r="G16" s="30">
         <f>('STT Report'!L435+'STT Report'!U435)/40</f>
-        <v>247.41</v>
+        <v>284.20500000000004</v>
       </c>
       <c r="H16" s="31">
         <f>E16+F16-G16</f>
-        <v>74.080000000000013</v>
+        <v>37.284999999999968</v>
       </c>
     </row>
     <row r="17" spans="3:13" ht="16.5" x14ac:dyDescent="0.45">
@@ -50279,11 +51743,11 @@
       </c>
       <c r="G17" s="30">
         <f>('STT Report'!M435+'STT Report'!V435)/40</f>
-        <v>325.70625000000001</v>
+        <v>363.68375000000003</v>
       </c>
       <c r="H17" s="31">
         <f>E17+F17-G17</f>
-        <v>-93.386250000000018</v>
+        <v>-131.36375000000004</v>
       </c>
     </row>
     <row r="18" spans="3:13" x14ac:dyDescent="0.35">
@@ -50300,11 +51764,11 @@
       </c>
       <c r="G18" s="36">
         <f>SUM(G15:G17)</f>
-        <v>868.31874999999991</v>
+        <v>979.99625000000003</v>
       </c>
       <c r="H18" s="37">
         <f>SUM(H15:H17)</f>
-        <v>-86.388749999999987</v>
+        <v>-198.06625000000003</v>
       </c>
     </row>
     <row r="19" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -50321,11 +51785,11 @@
       </c>
       <c r="G19" s="39">
         <f>G10+G14+G18</f>
-        <v>2266.2512500000003</v>
+        <v>2512.6862500000002</v>
       </c>
       <c r="H19" s="41">
         <f>H10+H14+H18</f>
-        <v>367.41874999999993</v>
+        <v>120.98374999999999</v>
       </c>
     </row>
     <row r="20" spans="3:13" x14ac:dyDescent="0.35">

--- a/STT Report Elite Marketing FTMO June.xlsx
+++ b/STT Report Elite Marketing FTMO June.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C9A1E56-F92F-42EA-93C2-092B031FD6D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B1421F-80B3-4DDD-9F8A-FBCC288E21F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4AEE6371-F34D-490E-9664-B5033CDC9B85}"/>
   </bookViews>
@@ -1911,22 +1911,22 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="4" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1938,11 +1938,11 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2312,44 +2312,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="91" t="s">
+      <c r="A1" s="92" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="92" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="88" t="s">
+      <c r="C1" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="88" t="s">
+      <c r="D1" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="88" t="s">
+      <c r="E1" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="88" t="s">
+      <c r="F1" s="93" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="91" t="s">
+      <c r="G1" s="92" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="88" t="s">
+      <c r="H1" s="93" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="70"/>
-      <c r="K1" s="91" t="s">
+      <c r="K1" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="89" t="s">
+      <c r="L1" s="92"/>
+      <c r="M1" s="92"/>
+      <c r="N1" s="92"/>
+      <c r="O1" s="97" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="90"/>
-      <c r="Q1" s="90"/>
-      <c r="R1" s="90"/>
+      <c r="P1" s="98"/>
+      <c r="Q1" s="98"/>
+      <c r="R1" s="98"/>
       <c r="S1" s="94" t="s">
         <v>10</v>
       </c>
@@ -2365,61 +2365,61 @@
       <c r="Y1" s="96"/>
       <c r="Z1" s="96"/>
       <c r="AA1" s="96"/>
-      <c r="AB1" s="92" t="s">
+      <c r="AB1" s="90" t="s">
         <v>76</v>
       </c>
-      <c r="AC1" s="92" t="s">
+      <c r="AC1" s="90" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="92" t="s">
+      <c r="AD1" s="90" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="92" t="s">
+      <c r="AE1" s="90" t="s">
         <v>15</v>
       </c>
-      <c r="AF1" s="92" t="s">
+      <c r="AF1" s="90" t="s">
         <v>16</v>
       </c>
-      <c r="AG1" s="92" t="s">
+      <c r="AG1" s="90" t="s">
         <v>17</v>
       </c>
       <c r="AH1" s="80">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="AI1" s="92" t="s">
+      <c r="AI1" s="90" t="s">
         <v>18</v>
       </c>
-      <c r="AJ1" s="92" t="s">
+      <c r="AJ1" s="90" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="92" t="s">
+      <c r="AK1" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="92" t="s">
+      <c r="AL1" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="92" t="s">
+      <c r="AM1" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="AN1" s="97" t="s">
+      <c r="AN1" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="AO1" s="97" t="s">
+      <c r="AO1" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="AP1" s="92" t="s">
+      <c r="AP1" s="90" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:42" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="91"/>
-      <c r="B2" s="91"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="91"/>
-      <c r="H2" s="88"/>
+      <c r="A2" s="92"/>
+      <c r="B2" s="92"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="93"/>
       <c r="I2" s="2" t="s">
         <v>26</v>
       </c>
@@ -2475,23 +2475,23 @@
       <c r="AA2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="AB2" s="93"/>
-      <c r="AC2" s="93"/>
-      <c r="AD2" s="93"/>
-      <c r="AE2" s="93"/>
-      <c r="AF2" s="93"/>
-      <c r="AG2" s="93"/>
+      <c r="AB2" s="91"/>
+      <c r="AC2" s="91"/>
+      <c r="AD2" s="91"/>
+      <c r="AE2" s="91"/>
+      <c r="AF2" s="91"/>
+      <c r="AG2" s="91"/>
       <c r="AH2" s="78" t="s">
         <v>77</v>
       </c>
-      <c r="AI2" s="93"/>
-      <c r="AJ2" s="93"/>
-      <c r="AK2" s="93"/>
-      <c r="AL2" s="93"/>
-      <c r="AM2" s="93"/>
-      <c r="AN2" s="98"/>
-      <c r="AO2" s="98"/>
-      <c r="AP2" s="93"/>
+      <c r="AI2" s="91"/>
+      <c r="AJ2" s="91"/>
+      <c r="AK2" s="91"/>
+      <c r="AL2" s="91"/>
+      <c r="AM2" s="91"/>
+      <c r="AN2" s="89"/>
+      <c r="AO2" s="89"/>
+      <c r="AP2" s="91"/>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A3" s="17">
@@ -50420,75 +50420,75 @@
       <c r="H425" s="6"/>
       <c r="I425" s="6"/>
       <c r="J425" s="6">
-        <f>SUM(J3:J424)</f>
+        <f t="shared" ref="J425:AA425" si="178">SUM(J3:J424)</f>
         <v>5195</v>
       </c>
       <c r="K425" s="6">
-        <f>SUM(K3:K424)</f>
+        <f t="shared" si="178"/>
         <v>13881</v>
       </c>
       <c r="L425" s="6">
-        <f>SUM(L3:L424)</f>
+        <f t="shared" si="178"/>
         <v>13071</v>
       </c>
       <c r="M425" s="6">
-        <f>SUM(M3:M424)</f>
+        <f t="shared" si="178"/>
         <v>17644</v>
       </c>
       <c r="N425" s="6">
-        <f>SUM(N3:N424)</f>
+        <f t="shared" si="178"/>
         <v>44596</v>
       </c>
       <c r="O425" s="6">
-        <f>SUM(O3:O424)</f>
+        <f t="shared" si="178"/>
         <v>20263</v>
       </c>
       <c r="P425" s="6">
-        <f>SUM(P3:P424)</f>
+        <f t="shared" si="178"/>
         <v>17341</v>
       </c>
       <c r="Q425" s="6">
-        <f>SUM(Q3:Q424)</f>
+        <f t="shared" si="178"/>
         <v>24544</v>
       </c>
       <c r="R425" s="6">
-        <f>SUM(R3:R424)</f>
+        <f t="shared" si="178"/>
         <v>62148</v>
       </c>
       <c r="S425" s="6">
-        <f>SUM(S3:S424)</f>
+        <f t="shared" si="178"/>
         <v>111939</v>
       </c>
       <c r="T425" s="6">
-        <f>SUM(T3:T424)</f>
+        <f t="shared" si="178"/>
         <v>1387.7</v>
       </c>
       <c r="U425" s="6">
-        <f>SUM(U3:U424)</f>
+        <f t="shared" si="178"/>
         <v>1306.8000000000004</v>
       </c>
       <c r="V425" s="6">
-        <f>SUM(V3:V424)</f>
+        <f t="shared" si="178"/>
         <v>1764.2500000000005</v>
       </c>
       <c r="W425" s="6">
-        <f>SUM(W3:W424)</f>
+        <f t="shared" si="178"/>
         <v>4458.7499999999991</v>
       </c>
       <c r="X425" s="6">
-        <f>SUM(X3:X424)</f>
+        <f t="shared" si="178"/>
         <v>2026.2999999999997</v>
       </c>
       <c r="Y425" s="6">
-        <f>SUM(Y3:Y424)</f>
+        <f t="shared" si="178"/>
         <v>1734.1000000000001</v>
       </c>
       <c r="Z425" s="6">
-        <f>SUM(Z3:Z424)</f>
+        <f t="shared" si="178"/>
         <v>2454.4</v>
       </c>
       <c r="AA425" s="6">
-        <f>SUM(AA3:AA424)</f>
+        <f t="shared" si="178"/>
         <v>6214.7999999999993</v>
       </c>
       <c r="AB425" s="6"/>
@@ -50593,92 +50593,92 @@
         <v>55</v>
       </c>
       <c r="J429" s="76">
-        <f t="shared" ref="J429:AF429" si="178">+J425/40</f>
+        <f t="shared" ref="J429:AF429" si="179">+J425/40</f>
         <v>129.875</v>
       </c>
       <c r="K429" s="77">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>347.02499999999998</v>
       </c>
       <c r="L429" s="77">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>326.77499999999998</v>
       </c>
       <c r="M429" s="77">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>441.1</v>
       </c>
       <c r="N429" s="76">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>1114.9000000000001</v>
       </c>
       <c r="O429" s="77">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>506.57499999999999</v>
       </c>
       <c r="P429" s="77">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>433.52499999999998</v>
       </c>
       <c r="Q429" s="77">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>613.6</v>
       </c>
       <c r="R429" s="76">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>1553.7</v>
       </c>
       <c r="S429" s="15">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>2798.4749999999999</v>
       </c>
       <c r="T429" s="15">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>34.692500000000003</v>
       </c>
       <c r="U429" s="15">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>32.670000000000009</v>
       </c>
       <c r="V429" s="15">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>44.10625000000001</v>
       </c>
       <c r="W429" s="15">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>111.46874999999997</v>
       </c>
       <c r="X429" s="15">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>50.657499999999992</v>
       </c>
       <c r="Y429" s="15">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>43.352500000000006</v>
       </c>
       <c r="Z429" s="15">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>61.36</v>
       </c>
       <c r="AA429" s="15">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>155.36999999999998</v>
       </c>
       <c r="AB429" s="15"/>
       <c r="AC429">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
       <c r="AD429">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
       <c r="AE429">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>266871.85649999965</v>
       </c>
       <c r="AF429">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
     </row>
@@ -50703,14 +50703,13 @@
     <filterColumn colId="25" showButton="0"/>
   </autoFilter>
   <mergeCells count="27">
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="AG1:AG2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
@@ -50723,13 +50722,14 @@
     <mergeCell ref="AE1:AE2"/>
     <mergeCell ref="AF1:AF2"/>
     <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AN1:AN2"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -50795,16 +50795,18 @@
         <v>47</v>
       </c>
       <c r="E7" s="27">
-        <v>683.22</v>
-      </c>
-      <c r="F7" s="28"/>
+        <v>1954</v>
+      </c>
+      <c r="F7" s="28">
+        <v>9472</v>
+      </c>
       <c r="G7" s="29">
         <f>('STT Report'!O425+'STT Report'!X425)/40</f>
         <v>557.23249999999996</v>
       </c>
       <c r="H7" s="30">
         <f>E7+F7-G7</f>
-        <v>125.98750000000007</v>
+        <v>10868.7675</v>
       </c>
     </row>
     <row r="8" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -50812,10 +50814,10 @@
         <v>48</v>
       </c>
       <c r="E8" s="27">
-        <v>183.66</v>
+        <v>1558</v>
       </c>
       <c r="F8" s="31">
-        <v>150</v>
+        <v>7217</v>
       </c>
       <c r="G8" s="29">
         <f>('STT Report'!P425+'STT Report'!Y425)/40</f>
@@ -50823,7 +50825,7 @@
       </c>
       <c r="H8" s="30">
         <f>E8+F8-G8</f>
-        <v>-143.21749999999997</v>
+        <v>8298.1224999999995</v>
       </c>
     </row>
     <row r="9" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -50831,16 +50833,18 @@
         <v>49</v>
       </c>
       <c r="E9" s="27">
-        <v>334.86</v>
-      </c>
-      <c r="F9" s="31"/>
+        <v>387</v>
+      </c>
+      <c r="F9" s="31">
+        <v>12655</v>
+      </c>
       <c r="G9" s="29">
         <f>('STT Report'!Q425+'STT Report'!Z425)/40</f>
         <v>674.96</v>
       </c>
       <c r="H9" s="30">
         <f>E9+F9-G9</f>
-        <v>-340.1</v>
+        <v>12367.04</v>
       </c>
     </row>
     <row r="10" spans="4:8" x14ac:dyDescent="0.35">
@@ -50849,11 +50853,11 @@
       </c>
       <c r="E10" s="33">
         <f>SUM(E7:E9)</f>
-        <v>1201.74</v>
+        <v>3899</v>
       </c>
       <c r="F10" s="34">
         <f>SUM(F7:F9)</f>
-        <v>150</v>
+        <v>29344</v>
       </c>
       <c r="G10" s="35">
         <f>SUM(G7:G9)</f>
@@ -50861,16 +50865,18 @@
       </c>
       <c r="H10" s="36">
         <f>SUM(H7:H9)</f>
-        <v>-357.32999999999993</v>
+        <v>31533.93</v>
       </c>
     </row>
     <row r="11" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="D11" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="E11" s="28"/>
+      <c r="E11" s="27">
+        <v>10997</v>
+      </c>
       <c r="F11" s="28">
-        <v>500</v>
+        <v>57979</v>
       </c>
       <c r="G11" s="72">
         <f>'STT Report'!J425/40</f>
@@ -50878,7 +50884,7 @@
       </c>
       <c r="H11" s="30">
         <f t="shared" ref="H11:H13" si="0">(E11+F11)-G11</f>
-        <v>370.125</v>
+        <v>68846.125</v>
       </c>
     </row>
     <row r="12" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -50908,7 +50914,7 @@
       <c r="E14" s="34"/>
       <c r="F14" s="34">
         <f>SUM(F11:F13)</f>
-        <v>500</v>
+        <v>57979</v>
       </c>
       <c r="G14" s="33">
         <f>SUM(G11:G13)</f>
@@ -50916,7 +50922,7 @@
       </c>
       <c r="H14" s="36">
         <f>SUM(H11:H13)</f>
-        <v>370.125</v>
+        <v>68846.125</v>
       </c>
     </row>
     <row r="15" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -50924,16 +50930,18 @@
         <v>51</v>
       </c>
       <c r="E15" s="27">
-        <v>228.12</v>
-      </c>
-      <c r="F15" s="28"/>
+        <v>1165</v>
+      </c>
+      <c r="F15" s="28">
+        <v>1335</v>
+      </c>
       <c r="G15" s="29">
         <f>('STT Report'!K425+'STT Report'!T425)/40</f>
         <v>381.71750000000003</v>
       </c>
       <c r="H15" s="30">
         <f>E15+F15-G15</f>
-        <v>-153.59750000000003</v>
+        <v>2118.2824999999998</v>
       </c>
     </row>
     <row r="16" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -50941,16 +50949,18 @@
         <v>52</v>
       </c>
       <c r="E16" s="27">
-        <v>321.49</v>
-      </c>
-      <c r="F16" s="31"/>
+        <v>1152</v>
+      </c>
+      <c r="F16" s="31">
+        <v>14695</v>
+      </c>
       <c r="G16" s="29">
         <f>('STT Report'!L425+'STT Report'!U425)/40</f>
         <v>359.44500000000005</v>
       </c>
       <c r="H16" s="30">
         <f>E16+F16-G16</f>
-        <v>-37.955000000000041</v>
+        <v>15487.555</v>
       </c>
     </row>
     <row r="17" spans="3:13" ht="16.5" x14ac:dyDescent="0.45">
@@ -50958,10 +50968,10 @@
         <v>53</v>
       </c>
       <c r="E17" s="27">
-        <v>82.32</v>
+        <v>2731</v>
       </c>
       <c r="F17" s="31">
-        <v>150</v>
+        <v>13608</v>
       </c>
       <c r="G17" s="29">
         <f>('STT Report'!M425+'STT Report'!V425)/40</f>
@@ -50969,7 +50979,7 @@
       </c>
       <c r="H17" s="30">
         <f>E17+F17-G17</f>
-        <v>-252.88625000000002</v>
+        <v>15853.793750000001</v>
       </c>
     </row>
     <row r="18" spans="3:13" x14ac:dyDescent="0.35">
@@ -50978,11 +50988,11 @@
       </c>
       <c r="E18" s="33">
         <f>SUM(E15+E16+E17)</f>
-        <v>631.93000000000006</v>
+        <v>5048</v>
       </c>
       <c r="F18" s="34">
         <f>SUM(F15:F17)</f>
-        <v>150</v>
+        <v>29638</v>
       </c>
       <c r="G18" s="35">
         <f>SUM(G15:G17)</f>
@@ -50990,7 +51000,7 @@
       </c>
       <c r="H18" s="36">
         <f>SUM(H15:H17)</f>
-        <v>-444.43875000000008</v>
+        <v>33459.631250000006</v>
       </c>
     </row>
     <row r="19" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -50999,11 +51009,11 @@
       </c>
       <c r="E19" s="38">
         <f>E10+E14+E18</f>
-        <v>1833.67</v>
+        <v>8947</v>
       </c>
       <c r="F19" s="39">
         <f>F10+F14+F18</f>
-        <v>800</v>
+        <v>116961</v>
       </c>
       <c r="G19" s="38">
         <f>G10+G14+G18</f>
@@ -51011,7 +51021,7 @@
       </c>
       <c r="H19" s="40">
         <f>H10+H14+H18</f>
-        <v>-431.64375000000001</v>
+        <v>133839.68625</v>
       </c>
     </row>
     <row r="20" spans="3:13" x14ac:dyDescent="0.35">
